--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Keyword Mapping'!$A$1:$M$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Current Page Inventory'!$A$1:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Current Page Inventory'!$A$1:$H$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Content Gap Roadmap'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cluster Summary'!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$10</definedName>
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CurrentPageInventoryTable" displayName="CurrentPageInventoryTable" ref="A1:H78" headerRowCount="1">
-  <autoFilter ref="A1:H78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CurrentPageInventoryTable" displayName="CurrentPageInventoryTable" ref="A1:H79" headerRowCount="1">
+  <autoFilter ref="A1:H79"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Path"/>
     <tableColumn id="2" name="Topic Cluster"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>None supplied</t>
+          <t>https://docs.google.com/spreadsheets/d/1_IeyaXe1fSbXmV8Z4MdVOigMIz-cgK2h/edit</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Build the first non-complete page on Content Gap Roadmap. Each online run checks the live sitemap and HTTP response, moves completed pages below the active queue, labels their deployment status and strikes them through.</t>
+          <t>The standard production command builds up to five active pages from the top of the Content Gap Roadmap, one at a time. After each page it checks the live sitemap and HTTP response, moves completed pages below the active queue, labels their deployment status and strikes them through.</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8851,7 +8851,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -8914,13 +8914,19 @@
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>broadband</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: / (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to resolve</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -8940,13 +8946,19 @@
       </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>broadband deals, best broadband deals, cheap broadband deals, uk broadband deals</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /deals (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to re</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8966,13 +8978,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>compare broadband deals, compare broadband providers, broadband comparison uk</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /compare (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -8992,13 +9010,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>broadband providers</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed t</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9018,9 +9042,15 @@
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -9040,9 +9070,15 @@
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to r</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9062,13 +9098,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>broadband speed test, check my broadband speed</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /speed-test (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -9088,13 +9130,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>broadband glossary terms explained, what is fttp broadband, what is a good broadband speed</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /broadband-glossary (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443):</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9114,9 +9162,15 @@
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /about (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to re</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9136,9 +9190,15 @@
       </c>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /contact (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9158,13 +9218,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>how we make money broadband picker</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /how-we-make-money (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -9184,9 +9250,15 @@
       </c>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /how-we-review-broadband (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9206,9 +9278,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /editorial-policy (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): F</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -9228,9 +9306,15 @@
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /privacy-policy (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fai</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9250,9 +9334,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /cookie-policy (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fail</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -9272,9 +9362,15 @@
       </c>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /terms (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to re</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9294,13 +9390,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>broadband providers for my area, broadband in my area, broadband postcode checker</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /postcode (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -9320,75 +9422,93 @@
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>broadband providers london, best broadband london</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /postcode/london (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fa</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>/postcode/bristol</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Trust &amp; research</t>
+          <t>Postcode &amp; location</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Research dashboard</t>
+          <t>City hub</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>uk broadband customer satisfaction</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>broadband providers bristol</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /postcode/bristol (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-business-broadband-providers-uk</t>
+          <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Business broadband</t>
+          <t>Trust &amp; research</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Research dashboard</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>best business broadband providers uk, business broadband providers</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>uk broadband customer satisfaction</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /research/uk-broadband-customer-satisfaction (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-phone-and-broadband-deals</t>
+          <t>/guides/best-business-broadband-providers-uk</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Phone &amp; bundles</t>
+          <t>Business broadband</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -9398,23 +9518,29 @@
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>phone and broadband deals, landline broadband deals</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>best business broadband providers uk, business broadband providers</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-business-broadband-providers-uk (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>/guides/satellite-broadband-uk</t>
+          <t>/guides/best-phone-and-broadband-deals</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Alternative access</t>
+          <t>Phone &amp; bundles</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -9424,44 +9550,56 @@
       </c>
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>satellite broadband uk</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
+          <t>phone and broadband deals, landline broadband deals</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-phone-and-broadband-deals (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>/providers/bt</t>
+          <t>/guides/satellite-broadband-uk</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Alternative access</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Provider page</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>bt broadband, bt broadband deals, bt broadband reviews</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>satellite broadband uk</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/satellite-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk',</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>/providers/sky</t>
+          <t>/providers/bt</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -9476,18 +9614,24 @@
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>sky broadband, sky broadband deals, sky broadband reviews</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
+          <t>bt broadband, bt broadband deals, bt broadband reviews</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/bt (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Faile</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>/providers/virgin-media</t>
+          <t>/providers/sky</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -9502,18 +9646,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>virgin media broadband, virgin media broadband deals, virgin media broadband reviews</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>sky broadband, sky broadband deals, sky broadband reviews</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fail</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>/providers/ee</t>
+          <t>/providers/virgin-media</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -9528,18 +9678,24 @@
       </c>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>ee broadband, ee broadband deals, ee broadband reviews</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+          <t>virgin media broadband, virgin media broadband deals, virgin media broadband reviews</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/virgin-media (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=4</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>/providers/talktalk</t>
+          <t>/providers/ee</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -9554,18 +9710,24 @@
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>talktalk broadband, talktalk broadband deals, talktalk broadband reviews</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>ee broadband, ee broadband deals, ee broadband reviews</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/ee (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Faile</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>/providers/plusnet</t>
+          <t>/providers/talktalk</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -9580,18 +9742,24 @@
       </c>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>plusnet broadband, plusnet broadband deals, plusnet broadband reviews</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+          <t>talktalk broadband, talktalk broadband deals, talktalk broadband reviews</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443):</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>/providers/vodafone</t>
+          <t>/providers/plusnet</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -9606,18 +9774,24 @@
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>vodafone broadband, vodafone broadband deals, vodafone broadband reviews</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>plusnet broadband, plusnet broadband deals, plusnet broadband reviews</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/plusnet (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): </t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>/providers/now-broadband</t>
+          <t>/providers/vodafone</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -9632,18 +9806,24 @@
       </c>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>now broadband broadband, now broadband broadband deals, now broadband broadband reviews</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>vodafone broadband, vodafone broadband deals, vodafone broadband reviews</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443):</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>/providers/hyperoptic</t>
+          <t>/providers/now-broadband</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -9658,18 +9838,24 @@
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>hyperoptic broadband, hyperoptic broadband deals, hyperoptic broadband reviews</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>now broadband broadband, now broadband broadband deals, now broadband broadband reviews</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/now-broadband (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>/providers/community-fibre</t>
+          <t>/providers/hyperoptic</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -9684,18 +9870,24 @@
       </c>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>community fibre broadband, community fibre broadband deals, community fibre broadband reviews</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>hyperoptic broadband, hyperoptic broadband deals, hyperoptic broadband reviews</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/hyperoptic (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>/providers/zen-internet</t>
+          <t>/providers/community-fibre</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -9710,18 +9902,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>zen internet broadband, zen internet broadband deals, zen internet broadband reviews</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>community fibre broadband, community fibre broadband deals, community fibre broadband reviews</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/community-fibre (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', por</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>/providers/toob</t>
+          <t>/providers/zen-internet</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -9736,44 +9934,56 @@
       </c>
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>toob broadband, toob broadband deals, toob broadband reviews</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+          <t>zen internet broadband, zen internet broadband deals, zen internet broadband reviews</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/zen-internet (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=4</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-sky</t>
+          <t>/providers/toob</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Provider vs comparison</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Comparison page</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>bt vs sky broadband</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t>toob broadband, toob broadband deals, toob broadband reviews</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/toob (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fai</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-virgin-media</t>
+          <t>/providers/compare/bt-vs-sky</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -9788,18 +9998,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>bt vs virgin media broadband</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+          <t>bt vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', p</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/sky-vs-vodafone</t>
+          <t>/providers/compare/bt-vs-virgin-media</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -9814,18 +10030,24 @@
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>sky vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
+          <t>bt vs virgin media broadband</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-virgin-media (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/ee-vs-bt</t>
+          <t>/providers/compare/sky-vs-vodafone</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9840,18 +10062,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>ee vs bt broadband</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+          <t>sky vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/sky-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/talktalk-vs-now-broadband</t>
+          <t>/providers/compare/ee-vs-bt</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -9866,18 +10094,24 @@
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>talktalk vs now broadband</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>ee vs bt broadband</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/ee-vs-bt (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', po</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/virgin-media-vs-vodafone</t>
+          <t>/providers/compare/talktalk-vs-now-broadband</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9892,18 +10126,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>virgin media vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+          <t>talktalk vs now broadband</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/talktalk-vs-now-broadband (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/sky-vs-virgin-media</t>
+          <t>/providers/compare/virgin-media-vs-vodafone</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -9918,18 +10158,24 @@
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>sky vs virgin media broadband</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
+          <t>virgin media vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/virgin-media-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandp</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/hyperoptic-vs-community-fibre</t>
+          <t>/providers/compare/sky-vs-virgin-media</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9944,18 +10190,24 @@
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>hyperoptic vs community fibre</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
+          <t>sky vs virgin media broadband</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/sky-vs-virgin-media (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-vodafone</t>
+          <t>/providers/compare/hyperoptic-vs-community-fibre</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -9970,18 +10222,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>bt vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>hyperoptic vs community fibre</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/hyperoptic-vs-community-fibre (Caused by NameResolutionError("HTTPSConnection(host='broad</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/ee-vs-sky</t>
+          <t>/providers/compare/bt-vs-vodafone</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -9996,18 +10254,24 @@
       </c>
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>ee vs sky broadband</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
+          <t>bt vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-talktalk</t>
+          <t>/providers/compare/ee-vs-sky</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10022,18 +10286,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>bt vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t>ee vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/ee-vs-sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', p</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/ee-vs-vodafone</t>
+          <t>/providers/compare/bt-vs-talktalk</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10048,18 +10318,24 @@
       </c>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>ee vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
+          <t>bt vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/sky-vs-talktalk</t>
+          <t>/providers/compare/ee-vs-vodafone</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10074,18 +10350,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>sky vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
+          <t>ee vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/ee-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/plusnet-vs-bt</t>
+          <t>/providers/compare/sky-vs-talktalk</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10100,18 +10382,24 @@
       </c>
       <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>plusnet vs bt broadband</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
+          <t>sky vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/sky-vs-talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/plusnet-vs-sky</t>
+          <t>/providers/compare/plusnet-vs-bt</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10126,18 +10414,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>plusnet vs sky broadband</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
+          <t>plusnet vs bt broadband</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/plusnet-vs-bt (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/vodafone-vs-talktalk</t>
+          <t>/providers/compare/plusnet-vs-sky</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10152,44 +10446,56 @@
       </c>
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>vodafone vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
+          <t>plusnet vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/plusnet-vs-sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>/guides/how-to-switch-broadband-uk</t>
+          <t>/providers/compare/vodafone-vs-talktalk</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Editorial guide</t>
+          <t>Provider vs comparison</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Comparison page</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>switch broadband provider, how to switch broadband provider uk</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
+          <t>vodafone vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/vodafone-vs-talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicke</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-deals-uk</t>
+          <t>/guides/how-to-switch-broadband-uk</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10204,14 +10510,24 @@
       </c>
       <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>switch broadband provider, how to switch broadband provider uk</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/how-to-switch-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-with-no-mid-contract-price-rise</t>
+          <t>/guides/best-broadband-deals-uk</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10226,18 +10542,20 @@
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>broadband deals with no mid contract price rise</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-deals-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk'</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-and-tv-deals</t>
+          <t>/guides/broadband-deals-with-no-mid-contract-price-rise</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10252,18 +10570,24 @@
       </c>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>best broadband and tv deals</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr"/>
+          <t>broadband deals with no mid contract price rise</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-with-no-mid-contract-price-rise (Caused by NameResolutionError("HTTPSConnection(host</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-under-20</t>
+          <t>/guides/best-broadband-and-tv-deals</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10278,18 +10602,24 @@
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>broadband deals under 20, broadband deals under 20 a month</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
+          <t>best broadband and tv deals</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-and-tv-deals (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-with-cashback</t>
+          <t>/guides/broadband-deals-under-20</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10304,18 +10634,24 @@
       </c>
       <c r="D57" s="3" t="inlineStr"/>
       <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>broadband deals with cashback</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr"/>
+          <t>broadband deals under 20, broadband deals under 20 a month</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-under-20 (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-with-no-setup-fee</t>
+          <t>/guides/broadband-deals-with-cashback</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10330,18 +10666,24 @@
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>broadband deals with no setup fee</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
+          <t>broadband deals with cashback</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-with-cashback (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-rolling-monthly-broadband-deals</t>
+          <t>/guides/broadband-deals-with-no-setup-fee</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10356,18 +10698,24 @@
       </c>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>rolling monthly broadband no contract</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr"/>
+          <t>broadband deals with no setup fee</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-with-no-setup-fee (Caused by NameResolutionError("HTTPSConnection(host='broadbandpic</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>/guides/full-fibre-broadband-explained</t>
+          <t>/guides/best-rolling-monthly-broadband-deals</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10382,18 +10730,24 @@
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>full fibre broadband explained</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
+          <t>rolling monthly broadband no contract</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-rolling-monthly-broadband-deals (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-speeds-explained</t>
+          <t>/guides/full-fibre-broadband-explained</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10408,18 +10762,24 @@
       </c>
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>broadband speeds explained</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr"/>
+          <t>full fibre broadband explained</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/full-fibre-broadband-explained (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>/guides/cheapest-broadband-uk</t>
+          <t>/guides/broadband-speeds-explained</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -10434,18 +10794,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>cheapest broadband uk, cheapest broadband deals uk</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
+          <t>broadband speeds explained</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-speeds-explained (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-working-from-home</t>
+          <t>/guides/cheapest-broadband-uk</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -10460,18 +10826,24 @@
       </c>
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>best broadband for working from home</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr"/>
+          <t>cheapest broadband uk, cheapest broadband deals uk</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/cheapest-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-students</t>
+          <t>/guides/best-broadband-for-working-from-home</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -10486,18 +10858,24 @@
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>best broadband for students</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
+          <t>best broadband for working from home</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-working-from-home (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-streaming</t>
+          <t>/guides/best-broadband-for-students</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -10512,18 +10890,24 @@
       </c>
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>best broadband for streaming</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
+          <t>best broadband for students</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-students (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-providers-uk</t>
+          <t>/guides/best-broadband-for-streaming</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -10538,18 +10922,24 @@
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>best broadband providers uk</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
+          <t>best broadband for streaming</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-streaming (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-price-rises-2026</t>
+          <t>/guides/best-broadband-providers-uk</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -10564,18 +10954,24 @@
       </c>
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>broadband price rises 2026</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr"/>
+          <t>best broadband providers uk</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-providers-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>/guides/can-i-leave-broadband-early-after-price-rise</t>
+          <t>/guides/broadband-price-rises-2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -10590,18 +10986,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>can i leave broadband contract early</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
+          <t>broadband price rises 2026</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-price-rises-2026 (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-without-phone-line</t>
+          <t>/guides/can-i-leave-broadband-early-after-price-rise</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -10616,18 +11018,24 @@
       </c>
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>broadband without landline, broadband without phone line</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr"/>
+          <t>can i leave broadband contract early</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/can-i-leave-broadband-early-after-price-rise (Caused by NameResolutionError("HTTPSConnection(host='b</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-5g-home-broadband-uk</t>
+          <t>/guides/broadband-without-phone-line</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -10642,18 +11050,24 @@
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>best 5g home broadband uk</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
+          <t>broadband without landline, broadband without phone line</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-without-phone-line (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-full-fibre-broadband-uk</t>
+          <t>/guides/best-5g-home-broadband-uk</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -10668,18 +11082,24 @@
       </c>
       <c r="D71" s="3" t="inlineStr"/>
       <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>best full fibre broadband uk</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr"/>
+          <t>best 5g home broadband uk</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-5g-home-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-gaming-uk</t>
+          <t>/guides/best-full-fibre-broadband-uk</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -10694,18 +11114,24 @@
       </c>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>best broadband for gaming uk</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
+          <t>best full fibre broadband uk</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-full-fibre-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-social-tariffs-uk</t>
+          <t>/guides/best-broadband-for-gaming-uk</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -10720,18 +11146,24 @@
       </c>
       <c r="D73" s="3" t="inlineStr"/>
       <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>broadband social tariffs uk</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr"/>
+          <t>best broadband for gaming uk</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-gaming-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-moving-house</t>
+          <t>/guides/broadband-social-tariffs-uk</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -10746,18 +11178,24 @@
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>broadband when moving house</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
+          <t>broadband social tariffs uk</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-social-tariffs-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-rural-areas-uk</t>
+          <t>/guides/broadband-moving-house</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -10772,18 +11210,24 @@
       </c>
       <c r="D75" s="3" t="inlineStr"/>
       <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>best broadband for rural areas uk</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr"/>
+          <t>broadband when moving house</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-moving-house (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk',</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-for-existing-customers</t>
+          <t>/guides/best-broadband-for-rural-areas-uk</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -10798,18 +11242,24 @@
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>staying with existing broadband provider deals</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>best broadband for rural areas uk</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-rural-areas-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpic</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>/guides/one-touch-switching-explained</t>
+          <t>/guides/broadband-for-existing-customers</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -10824,18 +11274,24 @@
       </c>
       <c r="D77" s="3" t="inlineStr"/>
       <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>one touch switching broadband explained</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr"/>
+          <t>staying with existing broadband provider deals</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-for-existing-customers (Caused by NameResolutionError("HTTPSConnection(host='broadbandpick</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-contract-end-rights</t>
+          <t>/guides/one-touch-switching-explained</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -10850,16 +11306,54 @@
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
+          <t>one touch switching broadband explained</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/one-touch-switching-explained (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>/guides/broadband-contract-end-rights</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
           <t>broadband contract end rights</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-contract-end-rights (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H78"/>
+  <autoFilter ref="A1:H79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13037,10 +13531,10 @@
         <v>29670</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>39.4</v>

--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Keyword Mapping'!$A$1:$M$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Current Page Inventory'!$A$1:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Current Page Inventory'!$A$1:$H$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Content Gap Roadmap'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cluster Summary'!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$10</definedName>
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <strike val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -86,6 +92,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -198,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CurrentPageInventoryTable" displayName="CurrentPageInventoryTable" ref="A1:H79" headerRowCount="1">
-  <autoFilter ref="A1:H79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CurrentPageInventoryTable" displayName="CurrentPageInventoryTable" ref="A1:H153" headerRowCount="1">
+  <autoFilter ref="A1:H153"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Path"/>
     <tableColumn id="2" name="Topic Cluster"/>
@@ -615,7 +627,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1_IeyaXe1fSbXmV8Z4MdVOigMIz-cgK2h/edit</t>
+          <t>None supplied</t>
         </is>
       </c>
     </row>
@@ -942,7 +954,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1170,7 +1182,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1626,7 +1638,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1797,7 +1809,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1854,7 +1866,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2082,7 +2094,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2139,7 +2151,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2253,7 +2265,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2310,7 +2322,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2367,7 +2379,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3108,7 +3120,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3222,7 +3234,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3621,7 +3633,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -4020,7 +4032,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4077,7 +4089,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -4248,7 +4260,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4305,7 +4317,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -5103,7 +5115,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -6640,7 +6652,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -7894,7 +7906,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Content gap — recommend new page</t>
+          <t>Existing page</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -8841,17 +8853,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -8912,26 +8924,30 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Compare Broadband Deals for Your Postcode | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Compare Broadband Deals for Your Postcode</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>6187</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>broadband</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: / (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to resolve</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>/deals</t>
+          <t>/compare</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -8941,29 +8957,33 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Deals hub</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
+          <t>Comparison tool</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Compare All UK Broadband Providers 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Compare UK Broadband Providers</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>12990</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>broadband deals, best broadband deals, cheap broadband deals, uk broadband deals</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /deals (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to re</t>
-        </is>
-      </c>
+          <t>compare broadband deals, compare broadband providers, broadband comparison uk</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>/compare</t>
+          <t>/deals</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -8973,24 +8993,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Comparison tool</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Deals hub</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals UK June 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>All UK Broadband Deals</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>7722</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>compare broadband deals, compare broadband providers, broadband comparison uk</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /compare (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to </t>
-        </is>
-      </c>
+          <t>broadband deals, best broadband deals, cheap broadband deals, uk broadband deals</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -9008,21 +9032,25 @@
           <t>Provider directory</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>UK Broadband Provider Reviews 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>UK Broadband Provider Reviews</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>14922</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>broadband providers</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed t</t>
-        </is>
-      </c>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9040,17 +9068,21 @@
           <t>Comparison directory</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Provider Comparisons UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Provider Comparison Guides</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>8496</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): </t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -9068,17 +9100,21 @@
           <t>Guides directory</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Guides &amp; Advice | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Guides</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>9904</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to r</t>
-        </is>
-      </c>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9096,53 +9132,51 @@
           <t>Interactive tool</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Free Broadband Speed Test UK | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Broadband speed test</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>5872</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>broadband speed test, check my broadband speed</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /speed-test (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed </t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>/broadband-glossary</t>
+          <t>/tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Glossary</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>broadband glossary terms explained, what is fttp broadband, what is a good broadband speed</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /broadband-glossary (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443):</t>
-        </is>
-      </c>
+          <t>broadband cost per mbps calculator</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9160,17 +9194,21 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>About BroadbandPicker — How We Compare Broadband Deals</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>About BroadbandPicker</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>3088</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /about (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to re</t>
-        </is>
-      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9188,418 +9226,474 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Contact BroadbandPicker | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>2543</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /contact (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to </t>
-        </is>
-      </c>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>/how-we-make-money</t>
+          <t>/privacy-policy</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Trust &amp; compliance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Privacy Policy | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>how we make money broadband picker</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /how-we-make-money (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): </t>
-        </is>
-      </c>
+        <v>3158</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>/how-we-review-broadband</t>
+          <t>/cookie-policy</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Trust &amp; compliance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Cookie Policy | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Cookie Policy</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>2755</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /how-we-review-broadband (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=</t>
-        </is>
-      </c>
+      <c r="H13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>/editorial-policy</t>
+          <t>/terms</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Trust &amp; compliance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Terms of Use | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Terms of Use</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>2938</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /editorial-policy (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): F</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>/privacy-policy</t>
+          <t>/broadband-glossary</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
+          <t>Glossary</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Glossary: Every Term Explained | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Glossary</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /privacy-policy (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fai</t>
-        </is>
-      </c>
+        <v>18917</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>broadband glossary terms explained, what is fttp broadband, what is a good broadband speed</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>/cookie-policy</t>
+          <t>/how-we-make-money</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Trust &amp; compliance</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>How BroadbandPicker Makes Money | Commercial Disclosure | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>How BroadbandPicker Makes Money</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /cookie-policy (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fail</t>
-        </is>
-      </c>
+        <v>4054</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>how we make money broadband picker</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>/terms</t>
+          <t>/how-we-review-broadband</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Trust &amp; compliance</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>How We Review and Compare Broadband | Our Methodology | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>How We Review and Compare Broadband</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>4904</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /terms (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to re</t>
-        </is>
-      </c>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>/postcode</t>
+          <t>/editorial-policy</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Trust &amp; compliance</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Availability hub</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Policy | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Policy</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>broadband providers for my area, broadband in my area, broadband postcode checker</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /postcode (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Failed to</t>
-        </is>
-      </c>
+        <v>3961</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>/postcode/london</t>
+          <t>/providers/bt</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>BT Broadband Review 2026 — Deals from £30.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>BT Broadband Review</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>5365</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>broadband providers london, best broadband london</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /postcode/london (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fa</t>
-        </is>
-      </c>
+          <t>bt broadband, bt broadband deals, bt broadband reviews</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>/postcode/bristol</t>
+          <t>/providers/sky</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Sky Broadband Review 2026 — Deals from £25.00/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Sky Broadband Review</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>5237</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>broadband providers bristol</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /postcode/bristol (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): F</t>
-        </is>
-      </c>
+          <t>sky broadband, sky broadband deals, sky broadband reviews</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
+          <t>/providers/virgin-media</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Trust &amp; research</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Research dashboard</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media Broadband Review 2026 — Deals from £28.00/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media Broadband Review</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>5354</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>uk broadband customer satisfaction</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /research/uk-broadband-customer-satisfaction (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
-        </is>
-      </c>
+          <t>virgin media broadband, virgin media broadband deals, virgin media broadband reviews</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-business-broadband-providers-uk</t>
+          <t>/providers/ee</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Business broadband</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>EE Broadband Review 2026 — Deals from £26.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>EE Broadband Review</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>5342</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>best business broadband providers uk, business broadband providers</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-business-broadband-providers-uk (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
-        </is>
-      </c>
+          <t>ee broadband, ee broadband deals, ee broadband reviews</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-phone-and-broadband-deals</t>
+          <t>/providers/talktalk</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Phone &amp; bundles</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>TalkTalk Broadband Review 2026 — Deals from £19.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>TalkTalk Broadband Review</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>5224</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>phone and broadband deals, landline broadband deals</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-phone-and-broadband-deals (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker</t>
-        </is>
-      </c>
+          <t>talktalk broadband, talktalk broadband deals, talktalk broadband reviews</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>/guides/satellite-broadband-uk</t>
+          <t>/providers/plusnet</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Alternative access</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Plusnet Broadband Review 2026 — Deals from £22.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Plusnet Broadband Review</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>5092</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>satellite broadband uk</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/satellite-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk',</t>
-        </is>
-      </c>
+          <t>plusnet broadband, plusnet broadband deals, plusnet broadband reviews</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>/providers/bt</t>
+          <t>/providers/vodafone</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -9612,26 +9706,30 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Vodafone Broadband Review 2026 — Deals from £24.00/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Vodafone Broadband Review</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
+        <v>5315</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>bt broadband, bt broadband deals, bt broadband reviews</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/bt (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Faile</t>
-        </is>
-      </c>
+          <t>vodafone broadband, vodafone broadband deals, vodafone broadband reviews</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>/providers/sky</t>
+          <t>/providers/now-broadband</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -9644,26 +9742,30 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>NOW Broadband Broadband Review 2026 — Deals from £17.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>NOW Broadband Broadband Review</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>5184</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>sky broadband, sky broadband deals, sky broadband reviews</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fail</t>
-        </is>
-      </c>
+          <t>now broadband broadband, now broadband broadband deals, now broadband broadband reviews</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>/providers/virgin-media</t>
+          <t>/providers/hyperoptic</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -9676,26 +9778,30 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Hyperoptic Broadband Review 2026 — Deals from £22.00/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Hyperoptic Broadband Review</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
+        <v>5083</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>virgin media broadband, virgin media broadband deals, virgin media broadband reviews</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/virgin-media (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=4</t>
-        </is>
-      </c>
+          <t>hyperoptic broadband, hyperoptic broadband deals, hyperoptic broadband reviews</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>/providers/ee</t>
+          <t>/providers/community-fibre</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -9708,26 +9814,30 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Community Fibre Broadband Review 2026 — Deals from £21.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Community Fibre Broadband Review</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>5187</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ee broadband, ee broadband deals, ee broadband reviews</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/ee (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Faile</t>
-        </is>
-      </c>
+          <t>community fibre broadband, community fibre broadband deals, community fibre broadband reviews</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>/providers/talktalk</t>
+          <t>/providers/zen-internet</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -9740,26 +9850,30 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Zen Internet Broadband Review 2026 — Deals from £34.99/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Zen Internet Broadband Review</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>5322</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>talktalk broadband, talktalk broadband deals, talktalk broadband reviews</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443):</t>
-        </is>
-      </c>
+          <t>zen internet broadband, zen internet broadband deals, zen internet broadband reviews</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>/providers/plusnet</t>
+          <t>/providers/toob</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -9772,26 +9886,30 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Toob Broadband Review 2026 — Deals from £22.00/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Toob Broadband Review</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>4994</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>plusnet broadband, plusnet broadband deals, plusnet broadband reviews</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/plusnet (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): </t>
-        </is>
-      </c>
+          <t>toob broadband, toob broadband deals, toob broadband reviews</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>/providers/vodafone</t>
+          <t>/providers/youfibre</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -9804,186 +9922,210 @@
           <t>Provider page</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>YouFibre Broadband Review 2026 — Deals from £20.00/mo | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>YouFibre Broadband Review</t>
+        </is>
+      </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>5177</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>vodafone broadband, vodafone broadband deals, vodafone broadband reviews</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443):</t>
-        </is>
-      </c>
+          <t>youfibre broadband</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>/providers/now-broadband</t>
+          <t>/providers/compare/bt-vs-sky</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Provider vs comparison</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Sky Broadband 2026 | Prices, Speeds and Value | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Sky Broadband: Which Is Better in 2026?</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>5727</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>now broadband broadband, now broadband broadband deals, now broadband broadband reviews</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/now-broadband (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=</t>
-        </is>
-      </c>
+          <t>bt vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>/providers/hyperoptic</t>
+          <t>/providers/compare/bt-vs-virgin-media</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Provider vs comparison</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>BT vs Virgin Media Broadband 2026 | Speed, Coverage and Cost | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>BT vs Virgin Media Broadband: Which Provider Should You Pick?</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>5861</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>hyperoptic broadband, hyperoptic broadband deals, hyperoptic broadband reviews</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/hyperoptic (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443</t>
-        </is>
-      </c>
+          <t>bt vs virgin media broadband</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>/providers/community-fibre</t>
+          <t>/providers/compare/sky-vs-vodafone</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Provider vs comparison</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Sky vs Vodafone Broadband 2026 | Price, Speed and Contracts | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Sky vs Vodafone Broadband: Which One Offers Better Value?</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>5686</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>community fibre broadband, community fibre broadband deals, community fibre broadband reviews</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/community-fibre (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', por</t>
-        </is>
-      </c>
+          <t>sky vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>/providers/zen-internet</t>
+          <t>/providers/compare/ee-vs-bt</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Provider vs comparison</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>EE vs BT Broadband 2026 | Reliability, Speed and Coverage | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>EE vs BT Broadband: Which Is Better for Reliability?</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>5639</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>zen internet broadband, zen internet broadband deals, zen internet broadband reviews</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/zen-internet (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=4</t>
-        </is>
-      </c>
+          <t>ee vs bt broadband</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>/providers/toob</t>
+          <t>/providers/compare/talktalk-vs-now-broadband</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Provider vs comparison</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>TalkTalk vs NOW Broadband 2026 | Cheapest Budget Broadband Compared | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>TalkTalk vs NOW Broadband: Which Budget Provider Is Better?</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>5686</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>toob broadband, toob broadband deals, toob broadband reviews</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/toob (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', port=443): Fai</t>
-        </is>
-      </c>
+          <t>talktalk vs now broadband</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-sky</t>
+          <t>/providers/compare/virgin-media-vs-vodafone</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -9996,26 +10138,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Vodafone Broadband 2026 | Compare Speed, Price and Coverage | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Vodafone Broadband: Speed vs Value</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>5642</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>bt vs sky broadband</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', p</t>
-        </is>
-      </c>
+          <t>virgin media vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-virgin-media</t>
+          <t>/providers/compare/sky-vs-virgin-media</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10028,26 +10174,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Sky vs Virgin Media Broadband 2026 | Compare Price, Speed and TV Value | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Sky vs Virgin Media Broadband: Which Is Better for Your Home?</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
+        <v>5731</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>bt vs virgin media broadband</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-virgin-media (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
-        </is>
-      </c>
+          <t>sky vs virgin media broadband</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/sky-vs-vodafone</t>
+          <t>/providers/compare/hyperoptic-vs-community-fibre</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -10060,26 +10210,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs Community Fibre 2026 | Full Fibre Compared | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs Community Fibre: Which Full-Fibre Provider Is Better?</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="n">
-        <v>0</v>
+        <v>5631</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>sky vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/sky-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
-        </is>
-      </c>
+          <t>hyperoptic vs community fibre</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/ee-vs-bt</t>
+          <t>/providers/compare/bt-vs-vodafone</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10092,26 +10246,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Vodafone Broadband 2026 | Compare Price, Speed and Coverage | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Vodafone Broadband: Coverage or Better Value?</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
+        <v>5497</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ee vs bt broadband</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/ee-vs-bt (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', po</t>
-        </is>
-      </c>
+          <t>bt vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/talktalk-vs-now-broadband</t>
+          <t>/providers/compare/ee-vs-sky</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -10124,26 +10282,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>EE vs Sky Broadband 2026 | Compare Reliability, Price and Bundles | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>EE vs Sky Broadband: Which Mainstream Provider Should You Choose?</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>5607</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>talktalk vs now broadband</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/talktalk-vs-now-broadband (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
-        </is>
-      </c>
+          <t>ee vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/virgin-media-vs-vodafone</t>
+          <t>/providers/compare/bt-vs-talktalk</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10156,26 +10318,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>BT vs TalkTalk Broadband 2026 | Compare Price, Coverage and Value | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>BT vs TalkTalk Broadband: Pay More for BT or Save With TalkTalk?</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>5785</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>virgin media vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/virgin-media-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandp</t>
-        </is>
-      </c>
+          <t>bt vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/sky-vs-virgin-media</t>
+          <t>/providers/compare/ee-vs-vodafone</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10188,26 +10354,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>EE vs Vodafone Broadband 2026 | Compare Reliability, Price and Bundles | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>EE vs Vodafone Broadband: Reliability or Lower-Cost Value?</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="n">
-        <v>0</v>
+        <v>5685</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>sky vs virgin media broadband</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/sky-vs-virgin-media (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker</t>
-        </is>
-      </c>
+          <t>ee vs vodafone broadband</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/hyperoptic-vs-community-fibre</t>
+          <t>/providers/compare/sky-vs-talktalk</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10220,26 +10390,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sky vs TalkTalk Broadband 2026 | Compare Price, Contracts and Value | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Sky vs TalkTalk Broadband: Which Is Better for Price and Everyday Use?</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="n">
-        <v>0</v>
+        <v>5715</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>hyperoptic vs community fibre</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/hyperoptic-vs-community-fibre (Caused by NameResolutionError("HTTPSConnection(host='broad</t>
-        </is>
-      </c>
+          <t>sky vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-vodafone</t>
+          <t>/providers/compare/plusnet-vs-bt</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10252,26 +10426,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Plusnet vs BT Broadband 2026 | Compare Price, Support and Coverage | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Plusnet vs BT Broadband: Better Value or Broader Premium Coverage?</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="n">
-        <v>0</v>
+        <v>5729</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>bt vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
-        </is>
-      </c>
+          <t>plusnet vs bt broadband</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/ee-vs-sky</t>
+          <t>/providers/compare/plusnet-vs-sky</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10284,26 +10462,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Plusnet vs Sky Broadband 2026 | Compare Price, Support and Bundles | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Plusnet vs Sky Broadband: Straightforward Value or Better Family Fit?</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="n">
-        <v>0</v>
+        <v>5631</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>ee vs sky broadband</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/ee-vs-sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', p</t>
-        </is>
-      </c>
+          <t>plusnet vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/bt-vs-talktalk</t>
+          <t>/providers/compare/vodafone-vs-talktalk</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10316,26 +10498,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Vodafone vs TalkTalk Broadband 2026 | Compare Price, Fibre Value and Fit | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Vodafone vs TalkTalk Broadband: Better Value or Better Bundle Logic?</t>
+        </is>
+      </c>
       <c r="F47" s="3" t="n">
-        <v>0</v>
+        <v>5691</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>bt vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/bt-vs-talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
-        </is>
-      </c>
+          <t>vodafone vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/ee-vs-vodafone</t>
+          <t>/providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -10348,26 +10534,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Plusnet Broadband 2026 | Price, Speed and Service | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Plusnet Broadband: Which Is Better in 2026?</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="n">
-        <v>0</v>
+        <v>6992</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>ee vs vodafone broadband</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/ee-vs-vodafone (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
-        </is>
-      </c>
+          <t>bt vs plusnet broadband</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/sky-vs-talktalk</t>
+          <t>/providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10380,26 +10570,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs YouFibre Broadband 2026 | Full Fibre Compared | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs YouFibre Broadband: Which Full-Fibre Provider Is Better in 2026?</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="n">
-        <v>0</v>
+        <v>6229</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>sky vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/sky-vs-talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
-        </is>
-      </c>
+          <t>hyperoptic vs youfibre broadband</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/plusnet-vs-bt</t>
+          <t>/providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -10412,26 +10606,30 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>EE vs TalkTalk Broadband 2026 | Deals, Speed and Service | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="n">
-        <v>0</v>
+        <v>6994</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>plusnet vs bt broadband</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/plusnet-vs-bt (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk</t>
-        </is>
-      </c>
+          <t>ee vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>/providers/compare/plusnet-vs-sky</t>
+          <t>/providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10444,58 +10642,66 @@
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky Broadband 2026 | Deals, Speed and Reviews | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky Broadband: Which Is Better in 2026?</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="n">
-        <v>0</v>
+        <v>7457</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>plusnet vs sky broadband</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/plusnet-vs-sky (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
-        </is>
-      </c>
+          <t>virgin media vs sky broadband</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>/providers/compare/vodafone-vs-talktalk</t>
+          <t>/guides/how-to-switch-broadband-uk</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Provider vs comparison</t>
+          <t>Editorial guide</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Comparison page</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>How to Switch Broadband UK 2026 | Step-by-Step Guide</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>How to Switch Broadband in the UK (2026 Guide)</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>vodafone vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /providers/compare/vodafone-vs-talktalk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicke</t>
-        </is>
-      </c>
+          <t>switch broadband provider, how to switch broadband provider uk</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>/guides/how-to-switch-broadband-uk</t>
+          <t>/guides/best-broadband-deals-uk</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -10508,26 +10714,26 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals UK June 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in the UK Right Now</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>switch broadband provider, how to switch broadband provider uk</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/how-to-switch-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
-        </is>
-      </c>
+        <v>5248</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-deals-uk</t>
+          <t>/guides/broadband-deals-with-no-mid-contract-price-rise</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10540,22 +10746,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Deals With No Mid-Contract Price Rise | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Deals With No Mid-Contract Price Rise UK 2026</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-deals-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk'</t>
-        </is>
-      </c>
+        <v>6412</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>broadband deals with no mid contract price rise</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-with-no-mid-contract-price-rise</t>
+          <t>/guides/best-broadband-and-tv-deals</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -10568,26 +10782,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband and TV Deals UK 2026 | Compare Bundles</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband and TV Deals in the UK for 2026</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="n">
-        <v>0</v>
+        <v>9512</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>broadband deals with no mid contract price rise</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-with-no-mid-contract-price-rise (Caused by NameResolutionError("HTTPSConnection(host</t>
-        </is>
-      </c>
+          <t>best broadband and tv deals</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-and-tv-deals</t>
+          <t>/guides/broadband-deals-under-20</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -10600,26 +10818,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Deals Under £20 UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Deals Under £20 UK 2026</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>6150</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>best broadband and tv deals</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-and-tv-deals (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
-        </is>
-      </c>
+          <t>broadband deals under 20, broadband deals under 20 a month</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-under-20</t>
+          <t>/guides/broadband-deals-with-cashback</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -10632,26 +10854,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Deals With Cashback UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Deals With Cashback UK 2026</t>
+        </is>
+      </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>6155</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>broadband deals under 20, broadband deals under 20 a month</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-under-20 (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk</t>
-        </is>
-      </c>
+          <t>broadband deals with cashback</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-with-cashback</t>
+          <t>/guides/broadband-deals-with-no-setup-fee</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -10664,26 +10890,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Deals With No Setup Fee UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Deals With No Setup Fee UK 2026</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>6235</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>broadband deals with cashback</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-with-cashback (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
-        </is>
-      </c>
+          <t>broadband deals with no setup fee</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-deals-with-no-setup-fee</t>
+          <t>/guides/best-rolling-monthly-broadband-deals</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -10696,26 +10926,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Best Rolling Monthly Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Best Rolling Monthly Broadband Deals UK 2026</t>
+        </is>
+      </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>5966</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>broadband deals with no setup fee</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-deals-with-no-setup-fee (Caused by NameResolutionError("HTTPSConnection(host='broadbandpic</t>
-        </is>
-      </c>
+          <t>rolling monthly broadband no contract</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-rolling-monthly-broadband-deals</t>
+          <t>/guides/full-fibre-broadband-explained</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -10728,26 +10962,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Full Fibre Broadband Explained | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Full Fibre Broadband Explained: Is FTTP Worth It?</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="n">
-        <v>0</v>
+        <v>5370</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>rolling monthly broadband no contract</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-rolling-monthly-broadband-deals (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
-        </is>
-      </c>
+          <t>full fibre broadband explained</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>/guides/full-fibre-broadband-explained</t>
+          <t>/guides/broadband-speeds-explained</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -10760,26 +10998,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Speeds Explained | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Speeds Explained: What Speed Do You Actually Need?</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="n">
-        <v>0</v>
+        <v>5464</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>full fibre broadband explained</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/full-fibre-broadband-explained (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker</t>
-        </is>
-      </c>
+          <t>broadband speeds explained</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-speeds-explained</t>
+          <t>/guides/cheapest-broadband-uk</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -10792,26 +11034,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Cheapest Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Cheapest Broadband Deals in the UK 2026</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="n">
-        <v>0</v>
+        <v>5245</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>broadband speeds explained</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-speeds-explained (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
-        </is>
-      </c>
+          <t>cheapest broadband uk, cheapest broadband deals uk</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>/guides/cheapest-broadband-uk</t>
+          <t>/guides/best-broadband-for-working-from-home</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -10824,26 +11070,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband for Working From Home | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband for Working From Home UK 2026</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="n">
-        <v>0</v>
+        <v>5364</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>cheapest broadband uk, cheapest broadband deals uk</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/cheapest-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk', </t>
-        </is>
-      </c>
+          <t>best broadband for working from home</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-working-from-home</t>
+          <t>/guides/best-broadband-for-students</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -10856,26 +11106,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband for Students UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband for Students UK 2026</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="n">
-        <v>0</v>
+        <v>6294</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>best broadband for working from home</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-working-from-home (Caused by NameResolutionError("HTTPSConnection(host='broadband</t>
-        </is>
-      </c>
+          <t>best broadband for students</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-students</t>
+          <t>/guides/best-broadband-for-streaming</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -10888,26 +11142,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband for Streaming UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband for Streaming UK 2026</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="n">
-        <v>0</v>
+        <v>6285</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>best broadband for students</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-students (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
-        </is>
-      </c>
+          <t>best broadband for streaming</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-streaming</t>
+          <t>/guides/best-broadband-providers-uk</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -10920,26 +11178,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Providers UK 2026 | Ranked by Speed, Price &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Providers UK 2026: Ranked and Reviewed</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="n">
-        <v>0</v>
+        <v>6992</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>best broadband for streaming</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-streaming (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
-        </is>
-      </c>
+          <t>best broadband providers uk</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-providers-uk</t>
+          <t>/guides/broadband-price-rises-2026</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -10952,26 +11214,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Price Rises 2026: Which Providers Are Putting Prices Up?</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Price Rises 2026: Every Provider Explained</t>
+        </is>
+      </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>7051</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>best broadband providers uk</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-providers-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
-        </is>
-      </c>
+          <t>broadband price rises 2026</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-price-rises-2026</t>
+          <t>/guides/can-i-leave-broadband-early-after-price-rise</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -10984,26 +11250,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Can I Leave Broadband Early After a Price Rise? | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Can I Leave Broadband Early After a Price Rise? UK Rules Explained</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="n">
-        <v>0</v>
+        <v>6439</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>broadband price rises 2026</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-price-rises-2026 (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.</t>
-        </is>
-      </c>
+          <t>can i leave broadband contract early</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>/guides/can-i-leave-broadband-early-after-price-rise</t>
+          <t>/guides/broadband-without-phone-line</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -11016,26 +11286,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Without a Phone Line UK 2026 | No Landline Needed</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Without a Phone Line UK 2026: Your Full Options</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>6559</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>can i leave broadband contract early</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/can-i-leave-broadband-early-after-price-rise (Caused by NameResolutionError("HTTPSConnection(host='b</t>
-        </is>
-      </c>
+          <t>broadband without landline, broadband without phone line</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-without-phone-line</t>
+          <t>/guides/best-5g-home-broadband-uk</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11048,26 +11322,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Best 5G Home Broadband UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Best 5G Home Broadband UK 2026</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="n">
-        <v>0</v>
+        <v>6070</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>broadband without landline, broadband without phone line</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-without-phone-line (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
-        </is>
-      </c>
+          <t>best 5g home broadband uk</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-5g-home-broadband-uk</t>
+          <t>/guides/best-full-fibre-broadband-uk</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -11080,26 +11358,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Best Full Fibre Broadband UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Best Full Fibre Broadband UK 2026</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>6188</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>best 5g home broadband uk</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-5g-home-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.u</t>
-        </is>
-      </c>
+          <t>best full fibre broadband uk</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-full-fibre-broadband-uk</t>
+          <t>/guides/best-broadband-for-gaming-uk</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -11112,26 +11394,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband for Gaming UK 2026 | Low Ping, High Speed</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband for Gaming UK 2026: Speed, Ping and Providers</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="n">
-        <v>0</v>
+        <v>6552</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>best full fibre broadband uk</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-full-fibre-broadband-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
-        </is>
-      </c>
+          <t>best broadband for gaming uk</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-gaming-uk</t>
+          <t>/guides/broadband-social-tariffs-uk</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -11144,26 +11430,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Social Tariffs UK 2026 | Cheap Broadband on Benefits</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Social Tariffs UK 2026: Who Qualifies and How to Apply</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="n">
-        <v>0</v>
+        <v>7552</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>best broadband for gaming uk</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-gaming-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.c</t>
-        </is>
-      </c>
+          <t>broadband social tariffs uk</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>/guides/broadband-social-tariffs-uk</t>
+          <t>/guides/broadband-moving-house</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -11176,26 +11466,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Moving House UK 2026 | Complete Checklist &amp; Guide</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Broadband When Moving House UK 2026: Complete Checklist</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="n">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>broadband social tariffs uk</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-social-tariffs-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co</t>
-        </is>
-      </c>
+          <t>broadband when moving house</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-moving-house</t>
+          <t>/guides/best-broadband-for-rural-areas-uk</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -11208,26 +11502,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband for Rural Areas UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband for Rural Areas UK 2026</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="n">
-        <v>0</v>
+        <v>6226</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>broadband when moving house</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-moving-house (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.co.uk',</t>
-        </is>
-      </c>
+          <t>best broadband for rural areas uk</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>/guides/best-broadband-for-rural-areas-uk</t>
+          <t>/guides/broadband-for-existing-customers</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -11240,26 +11538,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals for Existing Customers | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals for Existing Customers UK 2026</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="n">
-        <v>0</v>
+        <v>6153</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>best broadband for rural areas uk</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/best-broadband-for-rural-areas-uk (Caused by NameResolutionError("HTTPSConnection(host='broadbandpic</t>
-        </is>
-      </c>
+          <t>staying with existing broadband provider deals</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-for-existing-customers</t>
+          <t>/guides/one-touch-switching-explained</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -11272,26 +11574,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>One Touch Switching Explained | BroadbandPicker UK Guide</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>One Touch Switching Explained: How Broadband Switching Works in 2026</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="n">
-        <v>0</v>
+        <v>6335</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>staying with existing broadband provider deals</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-for-existing-customers (Caused by NameResolutionError("HTTPSConnection(host='broadbandpick</t>
-        </is>
-      </c>
+          <t>one touch switching broadband explained</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>/guides/one-touch-switching-explained</t>
+          <t>/guides/broadband-contract-end-rights</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -11304,26 +11610,30 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Contract End Rights UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Contract End Rights UK 2026: What Happens When Your Deal Ends</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="n">
-        <v>0</v>
+        <v>6373</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>one touch switching broadband explained</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/one-touch-switching-explained (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
-        </is>
-      </c>
+          <t>broadband contract end rights</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>/guides/broadband-contract-end-rights</t>
+          <t>/guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -11336,24 +11646,2476 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Static IP Business Broadband: Need and Cost Explained</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Static IP Business Broadband: When You Need One and How Much It Costs</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>7602</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>broadband contract end rights</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>HTTPSConnectionPool(host='broadbandpicker.co.uk', port=443): Max retries exceeded with url: /guides/broadband-contract-end-rights (Caused by NameResolutionError("HTTPSConnection(host='broadbandpicker.</t>
-        </is>
-      </c>
+          <t>static ip business broadband</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>/guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Student Broadband Cities Guide | Short-Term Deals</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Student Broadband Cities Guide: Short-Term and Rolling Deals</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>8705</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>student broadband cities guide</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>/guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Small Office Broadband Setup Checklist | UK Guide</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Small Office Broadband Setup: Router, Backup and Support Checklist</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>8222</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>small office broadband setup</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>/guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Broadband for Landlords and HMOs | UK Guide</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Broadband for Landlords and HMOs: What to Set Up and Who Pays</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>8831</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>broadband for landlords hmo</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>/guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Leased Line Cost UK: Small Business Price Guide</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Leased Line Cost UK: What Small Businesses Actually Pay</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>8942</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>leased line cost uk</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>/guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Starlink vs Openreach Broadband: UK Comparison</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Starlink vs Openreach Broadband: When Satellite Makes Sense in the UK</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>8995</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>starlink vs openreach broadband</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>/guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Editorial guide</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>January Broadband Deals UK: Switching Guide</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>January Broadband Deals UK: New-Year Switching Guide</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>8666</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>january broadband deals</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>/guides/best-business-broadband-providers-uk</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Best Business Broadband Providers UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Best business broadband providers in the UK</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>4937</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>best business broadband providers uk, business broadband providers</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>/postcode</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Availability hub</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Broadband by Postcode UK | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in your area</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>broadband providers for my area, broadband in my area, broadband postcode checker</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>/guides/best-phone-and-broadband-deals</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Phone &amp; bundles</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Best Phone and Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Best phone and broadband deals in the UK</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>4499</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>phone and broadband deals, landline broadband deals</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>/providers/bt/deals</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>BT Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>BT broadband deals</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>4563</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>/providers/sky/deals</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Sky Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Sky broadband deals</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>4561</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>/providers/ee/deals</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>EE Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>EE broadband deals</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>4565</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>/providers/virgin-media/deals</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Virgin Media Broadband Deals UK 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Virgin Media broadband deals</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Trust &amp; research</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Research dashboard</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>UK Broadband Satisfaction Research 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>UK broadband customer satisfaction: evidence dashboard</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>4343</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>uk broadband customer satisfaction</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>/guides/satellite-broadband-uk</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Alternative access</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Satellite Broadband UK Guide 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Satellite broadband in the UK: providers, costs and alternatives</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>4410</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>satellite broadband uk</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/london</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Providers in London 2026 | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in London</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>4414</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>broadband providers london, best broadband london</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/sheffield</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Providers Sheffield: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>5435</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>broadband providers sheffield</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Providers Edinburgh: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>5459</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>broadband providers edinburgh</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Providers Glasgow: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>5508</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>broadband providers glasgow</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Providers Liverpool: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>5453</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>broadband providers liverpool</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/leeds</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Providers Leeds: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>5454</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>broadband providers leeds</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/bristol</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Providers Bristol: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>5536</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>broadband providers bristol</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Broadband Providers Birmingham: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>5604</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>broadband providers birmingham</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/manchester</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Providers Manchester: Coverage and Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>5605</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>broadband providers manchester</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/e1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>E1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Whitechapel ( E1 )</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>7722</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/e2</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>E2 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Bethnal Green ( E2 )</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>7761</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/ec1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>EC1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Clerkenwell ( EC1 )</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>7391</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/n1</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>N1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Islington ( N1 )</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>7722</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/nw1</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>NW1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Camden ( NW1 )</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>7722</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/se1</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>SE1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Southwark ( SE1 )</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>7395</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/sw1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>SW1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Westminster ( SW1 )</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/w1</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>W1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Mayfair ( W1 )</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/w5</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>W5 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Ealing ( W5 )</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>7392</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/wc1</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>WC1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Bloomsbury ( WC1 )</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>7391</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/m1</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>M1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Manchester City Centre ( M1 )</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/m4</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>M4 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Northern Quarter ( M4 )</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>7098</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/m14</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>M14 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Fallowfield ( M14 )</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>7059</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/b1</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>B1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Birmingham City Centre ( B1 )</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/b15</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>B15 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Edgbaston ( B15 )</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>7059</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/ls1</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>LS1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Leeds City Centre ( LS1 )</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>7133</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/ls2</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>LS2 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Leeds ( LS2 )</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>7053</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/l1</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>L1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Liverpool City Centre ( L1 )</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/l8</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>L8 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Toxteth ( L8 )</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>6698</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/s1</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>S1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Sheffield City Centre ( S1 )</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>7135</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr"/>
+      <c r="H123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/bs1</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>BS1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Bristol City Centre ( BS1 )</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/bs3</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>BS3 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Bedminster ( BS3 )</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>7059</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr"/>
+      <c r="H125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/eh1</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>EH1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Edinburgh City Centre ( EH1 )</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>7490</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/g1</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>G1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Glasgow City Centre ( G1 )</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>7135</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/cf10</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>CF10 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Cardiff City Centre ( CF10 )</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>7135</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/bt1</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>BT1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Belfast City Centre ( BT1 )</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>6778</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/ox1</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>OX1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Oxford City Centre ( OX1 )</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/cb1</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>CB1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Cambridge City Centre ( CB1 )</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>7490</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr"/>
+      <c r="H131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/ne1</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>NE1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Newcastle City Centre ( NE1 )</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/ng1</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>NG1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Nottingham City Centre ( NG1 )</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/le1</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>LE1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Leicester City Centre ( LE1 )</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/cv1</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>CV1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Coventry City Centre ( CV1 )</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/so14</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>SO14 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Southampton City Centre ( SO14 )</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>7465</v>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/po1</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>PO1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Portsmouth City Centre ( PO1 )</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/bn1</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>BN1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Brighton City Centre ( BN1 )</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/ct1</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>CT1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Canterbury ( CT1 )</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>6698</v>
+      </c>
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/kt1</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>KT1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Kingston upon Thames ( KT1 )</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>7474</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/cr0</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>CR0 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Croydon ( CR0 )</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>7394</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr"/>
+      <c r="H141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/ha1</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>HA1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Harrow ( HA1 )</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>7053</v>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/ub1</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>UB1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Southall ( UB1 )</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>7055</v>
+      </c>
+      <c r="G143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/en1</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>EN1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Enfield ( EN1 )</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>7053</v>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/rm1</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>RM1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Romford ( RM1 )</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>7053</v>
+      </c>
+      <c r="G145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/da1</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>DA1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Dartford ( DA1 )</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>7059</v>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/me1</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>ME1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Rochester ( ME1 )</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>6698</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr"/>
+      <c r="H147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/sl1</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>SL1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Slough ( SL1 )</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>7057</v>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/rg1</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>RG1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Reading Town Centre ( RG1 )</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G149" s="3" t="inlineStr"/>
+      <c r="H149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/gu1</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>GU1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Guildford ( GU1 )</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>7059</v>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/mk1</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>MK1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Milton Keynes ( MK1 )</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>7098</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr"/>
+      <c r="H151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>/postcode/lu1</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>LU1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Luton ( LU1 )</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>7053</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>/postcode/sg1</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Postcode prefix page</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>SG1 Broadband Deals | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Best Broadband Deals in Stevenage ( SG1 )</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>7055</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr"/>
+      <c r="H153" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H79"/>
+  <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -11371,7 +14133,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
@@ -11464,40 +14226,44 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
+          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Provider vs comparison</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Comparison page</t>
+          <t>Interactive tool</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>hyperoptic vs youfibre broadband</t>
+          <t>broadband cost per mbps calculator</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -11505,14 +14271,14 @@
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>37</v>
+        <v>27.6</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 14); niche combined demand (140/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11522,40 +14288,44 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
+          <t>https://broadbandpicker.co.uk/providers/onestream</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>City hub</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>broadband providers sheffield</t>
+          <t>onestream broadband</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>590</v>
+        <v>880</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -11563,14 +14333,14 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>66.8</v>
+        <v>59.4</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 19); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11580,23 +14350,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
+          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Business broadband</t>
+          <t>Affordability</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11606,29 +14380,29 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>static ip business broadband</t>
+          <t>no credit check broadband</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>480</v>
+        <v>1900</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>66.3</v>
+        <v>59.3</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>46.1</v>
+        <v>34.8</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 24); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11638,40 +14412,44 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
+          <t>https://broadbandpicker.co.uk/providers/brsk</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Use cases &amp; lifestyle</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>student broadband cities guide</t>
+          <t>brsk broadband</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>320</v>
+        <v>1900</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -11679,14 +14457,14 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>59</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>36.2</v>
+        <v>28.5</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 18); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11696,55 +14474,59 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
+          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Technology &amp; speeds</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>City hub</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>broadband providers edinburgh</t>
+          <t>fttp vs fttc explained</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>65.8</v>
+        <v>58.4</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>40</v>
+        <v>27.8</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 21); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11754,23 +14536,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
+          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Business broadband</t>
+          <t>Technology &amp; speeds</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -11780,29 +14566,29 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>small office broadband setup</t>
+          <t>best mesh wifi for broadband router</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>390</v>
+        <v>1300</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>65.8</v>
+        <v>58.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>41.9</v>
+        <v>34</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 22); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11812,40 +14598,44 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
+          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Provider vs comparison</t>
+          <t>Affordability</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Comparison page</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>bt vs plusnet broadband</t>
+          <t>broadband for universal credit</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>320</v>
+        <v>720</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -11853,14 +14643,14 @@
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>65.5</v>
+        <v>58.2</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>36.4</v>
+        <v>27.5</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 19); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11870,40 +14660,44 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
+          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>City hub</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>broadband providers glasgow</t>
+          <t>gigaclear broadband</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>880</v>
+        <v>2400</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -11911,14 +14705,14 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>65.5</v>
+        <v>56.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>40.2</v>
+        <v>27.9</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11928,40 +14722,44 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
+          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>City hub</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>broadband providers liverpool</t>
+          <t>cuckoo broadband broadband</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>880</v>
+        <v>2900</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -11969,14 +14767,14 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>65.5</v>
+        <v>56.5</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>40.1</v>
+        <v>27.9</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -11986,23 +14784,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
+          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Use cases &amp; lifestyle</t>
+          <t>Deals &amp; pricing</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -12012,29 +14814,29 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>broadband for landlords hmo</t>
+          <t>black friday broadband deals</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>480</v>
+        <v>5400</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>36.6</v>
+        <v>37</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -12044,40 +14846,44 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
+          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Postcode &amp; location</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>City hub</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>broadband providers leeds</t>
+          <t>shell energy broadband broadband</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -12085,14 +14891,14 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40.3</v>
+        <v>28</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 23); strong combined demand (1,000/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -12102,55 +14908,59 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
+          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Provider vs comparison</t>
+          <t>Trust &amp; research</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Comparison page</t>
+          <t>Research page</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>ee vs talktalk broadband</t>
+          <t>best customer service broadband provider</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>390</v>
+        <v>880</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>65</v>
+        <v>55.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>36.4</v>
+        <v>27.8</v>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -12160,1215 +14970,1259 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>Planned — not live</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Trust &amp; research</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>broadband complaints ombudsman</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 26); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>hyperoptic vs youfibre broadband</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 14); niche combined demand (140/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>broadband providers sheffield</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>590</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 19); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>static ip business broadband</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 24); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Student broadband by university city: short-term and rolling deals</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Use cases &amp; lifestyle</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>student broadband cities guide</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 18); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers edinburgh</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 21); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>small office broadband setup</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 22); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>bt vs plusnet broadband</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 19); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>broadband providers glasgow</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>880</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers liverpool</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Use cases &amp; lifestyle</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>broadband for landlords hmo</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers leeds</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 23); strong combined demand (1,000/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>ee vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
           <t>https://broadbandpicker.co.uk/postcode/bristol</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>broadband providers bristol</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I27" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L27" s="4" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M27" s="4" t="n">
         <v>40.8</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>broadband providers birmingham</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I28" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J28" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L28" s="5" t="n">
         <v>64.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M28" s="5" t="n">
         <v>41.1</v>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 25); strong combined demand (1,600/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/manchester</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Manchester: coverage and best deals</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>broadband providers manchester</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I29" s="4" t="n">
         <v>1900</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L29" s="4" t="n">
         <v>64.2</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M29" s="4" t="n">
         <v>41.2</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Leased line cost UK: what small businesses actually pay</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Business broadband</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>leased line cost uk</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I30" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J30" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L30" s="5" t="n">
         <v>63.3</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M30" s="5" t="n">
         <v>58.6</v>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 30); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Alternative access</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>starlink vs openreach broadband</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I31" s="4" t="n">
         <v>590</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J31" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L31" s="4" t="n">
         <v>62.9</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M31" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>virgin media vs sky broadband</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I32" s="5" t="n">
         <v>880</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J32" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L32" s="5" t="n">
         <v>62.8</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M32" s="5" t="n">
         <v>36.2</v>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 25); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>January broadband deals UK: new-year switching guide</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Deals &amp; pricing</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>january broadband deals</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I33" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J33" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L33" s="4" t="n">
         <v>61.7</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M33" s="4" t="n">
         <v>36.9</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 28); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Interactive tool</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>broadband cost per mbps calculator</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/onestream</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>onestream broadband</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>880</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Affordability</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>no credit check broadband</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/brsk</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>brsk broadband</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Technology &amp; speeds</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>fttp vs fttc explained</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Technology &amp; speeds</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>best mesh wifi for broadband router</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>youfibre broadband</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Affordability</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>broadband for universal credit</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>720</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>gigaclear broadband</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>youfibre broadband</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="n">
+      <c r="L34" s="5" t="n">
         <v>56.6</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M34" s="5" t="n">
         <v>28.7</v>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); strong combined demand (4,400/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>cuckoo broadband broadband</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Deals &amp; pricing</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>black friday broadband deals</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>5400</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>shell energy broadband broadband</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Trust &amp; research</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Research page</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>best customer service broadband provider</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Trust &amp; research</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>broadband complaints ombudsman</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 26); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -13443,10 +16297,10 @@
         <v>819842</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>30.8</v>
@@ -13487,10 +16341,10 @@
         <v>286710</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>38.9</v>
@@ -13531,10 +16385,10 @@
         <v>29670</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>39.4</v>
@@ -13575,10 +16429,10 @@
         <v>23490</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>37.9</v>
@@ -13597,10 +16451,10 @@
         <v>12290</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>36.2</v>
@@ -13641,10 +16495,10 @@
         <v>11900</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>36.9</v>
@@ -13685,10 +16539,10 @@
         <v>4490</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>51.5</v>
@@ -13751,10 +16605,10 @@
         <v>2990</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>36</v>

--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -94,10 +94,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7722</v>
+        <v>11360</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9904</v>
+        <v>10163</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -9168,9 +9168,19 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Broadband Cost Calculator | True Monthly Cost UK | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Broadband cost calculator</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5349</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>broadband cost per mbps calculator</t>
@@ -9501,7 +9511,7 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5365</v>
+        <v>5489</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -9537,7 +9547,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5237</v>
+        <v>5361</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -9573,7 +9583,7 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5354</v>
+        <v>5484</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -9609,7 +9619,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5342</v>
+        <v>5466</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -9645,7 +9655,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5224</v>
+        <v>5348</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -9681,7 +9691,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5092</v>
+        <v>5218</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -9717,7 +9727,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5315</v>
+        <v>5439</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -9753,7 +9763,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5184</v>
+        <v>5314</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -9789,7 +9799,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5083</v>
+        <v>5205</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -9825,7 +9835,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5187</v>
+        <v>5311</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -9861,7 +9871,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5322</v>
+        <v>5452</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -9897,7 +9907,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>4994</v>
+        <v>5118</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -9933,7 +9943,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5177</v>
+        <v>5301</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -12541,7 +12551,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>7722</v>
+        <v>9059</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
@@ -12573,7 +12583,7 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>7761</v>
+        <v>9100</v>
       </c>
       <c r="G105" s="3" t="inlineStr"/>
       <c r="H105" s="3" t="inlineStr"/>
@@ -12605,7 +12615,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>7391</v>
+        <v>8600</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
@@ -12637,7 +12647,7 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>7722</v>
+        <v>9059</v>
       </c>
       <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="3" t="inlineStr"/>
@@ -12669,7 +12679,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>7722</v>
+        <v>9059</v>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
@@ -12701,7 +12711,7 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>7395</v>
+        <v>8604</v>
       </c>
       <c r="G109" s="3" t="inlineStr"/>
       <c r="H109" s="3" t="inlineStr"/>
@@ -12733,7 +12743,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>7750</v>
+        <v>9093</v>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
@@ -12765,7 +12775,7 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>7750</v>
+        <v>9093</v>
       </c>
       <c r="G111" s="3" t="inlineStr"/>
       <c r="H111" s="3" t="inlineStr"/>
@@ -12797,7 +12807,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>7392</v>
+        <v>8603</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
@@ -12829,7 +12839,7 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>7391</v>
+        <v>8600</v>
       </c>
       <c r="G113" s="3" t="inlineStr"/>
       <c r="H113" s="3" t="inlineStr"/>
@@ -12861,7 +12871,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
@@ -12893,7 +12903,7 @@
         </is>
       </c>
       <c r="F115" s="3" t="n">
-        <v>7098</v>
+        <v>8175</v>
       </c>
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="3" t="inlineStr"/>
@@ -12925,7 +12935,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>7059</v>
+        <v>8134</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
@@ -12957,7 +12967,7 @@
         </is>
       </c>
       <c r="F117" s="3" t="n">
-        <v>7494</v>
+        <v>8705</v>
       </c>
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr"/>
@@ -12989,7 +12999,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>7059</v>
+        <v>8134</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
@@ -13021,7 +13031,7 @@
         </is>
       </c>
       <c r="F119" s="3" t="n">
-        <v>7133</v>
+        <v>8212</v>
       </c>
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="3" t="inlineStr"/>
@@ -13053,7 +13063,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>7053</v>
+        <v>8130</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
@@ -13085,7 +13095,7 @@
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="3" t="inlineStr"/>
@@ -13117,7 +13127,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>6698</v>
+        <v>7641</v>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
@@ -13149,7 +13159,7 @@
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>7135</v>
+        <v>8212</v>
       </c>
       <c r="G123" s="3" t="inlineStr"/>
       <c r="H123" s="3" t="inlineStr"/>
@@ -13181,7 +13191,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>7494</v>
+        <v>8705</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
@@ -13213,7 +13223,7 @@
         </is>
       </c>
       <c r="F125" s="3" t="n">
-        <v>7059</v>
+        <v>8134</v>
       </c>
       <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="3" t="inlineStr"/>
@@ -13245,7 +13255,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>7490</v>
+        <v>8701</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
@@ -13277,7 +13287,7 @@
         </is>
       </c>
       <c r="F127" s="3" t="n">
-        <v>7135</v>
+        <v>8212</v>
       </c>
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="3" t="inlineStr"/>
@@ -13309,7 +13319,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>7135</v>
+        <v>8212</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
@@ -13341,7 +13351,7 @@
         </is>
       </c>
       <c r="F129" s="3" t="n">
-        <v>6778</v>
+        <v>7723</v>
       </c>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr"/>
@@ -13373,7 +13383,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>7494</v>
+        <v>8705</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
@@ -13405,7 +13415,7 @@
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>7490</v>
+        <v>8701</v>
       </c>
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="3" t="inlineStr"/>
@@ -13437,7 +13447,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
@@ -13469,7 +13479,7 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr"/>
@@ -13501,7 +13511,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
@@ -13533,7 +13543,7 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr"/>
@@ -13565,7 +13575,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>7465</v>
+        <v>8670</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
@@ -13597,7 +13607,7 @@
         </is>
       </c>
       <c r="F137" s="3" t="n">
-        <v>7139</v>
+        <v>8216</v>
       </c>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
@@ -13629,7 +13639,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>7494</v>
+        <v>8705</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
@@ -13661,7 +13671,7 @@
         </is>
       </c>
       <c r="F139" s="3" t="n">
-        <v>6698</v>
+        <v>7641</v>
       </c>
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="3" t="inlineStr"/>
@@ -13693,7 +13703,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>7474</v>
+        <v>8685</v>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
@@ -13725,7 +13735,7 @@
         </is>
       </c>
       <c r="F141" s="3" t="n">
-        <v>7394</v>
+        <v>8603</v>
       </c>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr"/>
@@ -13757,7 +13767,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>7053</v>
+        <v>8130</v>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
@@ -13789,7 +13799,7 @@
         </is>
       </c>
       <c r="F143" s="3" t="n">
-        <v>7055</v>
+        <v>8130</v>
       </c>
       <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="3" t="inlineStr"/>
@@ -13821,7 +13831,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>7053</v>
+        <v>8130</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
@@ -13853,7 +13863,7 @@
         </is>
       </c>
       <c r="F145" s="3" t="n">
-        <v>7053</v>
+        <v>8130</v>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
@@ -13885,7 +13895,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>7059</v>
+        <v>8134</v>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
@@ -13917,7 +13927,7 @@
         </is>
       </c>
       <c r="F147" s="3" t="n">
-        <v>6698</v>
+        <v>7641</v>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr"/>
@@ -13949,7 +13959,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>7057</v>
+        <v>8134</v>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
@@ -13981,7 +13991,7 @@
         </is>
       </c>
       <c r="F149" s="3" t="n">
-        <v>7494</v>
+        <v>8705</v>
       </c>
       <c r="G149" s="3" t="inlineStr"/>
       <c r="H149" s="3" t="inlineStr"/>
@@ -14013,7 +14023,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>7059</v>
+        <v>8134</v>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
@@ -14045,7 +14055,7 @@
         </is>
       </c>
       <c r="F151" s="3" t="n">
-        <v>7098</v>
+        <v>8175</v>
       </c>
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="3" t="inlineStr"/>
@@ -14077,7 +14087,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>7053</v>
+        <v>8130</v>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
@@ -14109,7 +14119,7 @@
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>7055</v>
+        <v>8130</v>
       </c>
       <c r="G153" s="3" t="inlineStr"/>
       <c r="H153" s="3" t="inlineStr"/>
@@ -14236,34 +14246,34 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
+          <t>https://broadbandpicker.co.uk/providers/onestream</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Interactive tool</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>broadband cost per mbps calculator</t>
+          <t>onestream broadband</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>210</v>
+        <v>880</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -14271,14 +14281,14 @@
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27.6</v>
+        <v>28</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14298,49 +14308,49 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/onestream</t>
+          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+          <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Affordability</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Provider page</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>onestream broadband</t>
+          <t>no credit check broadband</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>880</v>
+        <v>1900</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>28</v>
+        <v>34.8</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14360,49 +14370,49 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
+          <t>https://broadbandpicker.co.uk/providers/brsk</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Affordability</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>no credit check broadband</t>
+          <t>brsk broadband</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>1900</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>59.3</v>
+        <v>59</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>34.8</v>
+        <v>28.5</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14422,31 +14432,31 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/brsk</t>
+          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Technology &amp; speeds</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Provider page</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>brsk broadband</t>
+          <t>fttp vs fttc explained</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1900</v>
+        <v>880</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>20</v>
@@ -14457,14 +14467,14 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>59</v>
+        <v>58.4</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14484,12 +14494,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
+          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -14504,29 +14514,29 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>fttp vs fttc explained</t>
+          <t>best mesh wifi for broadband router</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>880</v>
+        <v>1300</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
         <v>58.4</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>27.8</v>
+        <v>34</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14546,17 +14556,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
+          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Technology &amp; speeds</t>
+          <t>Affordability</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -14566,29 +14576,29 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>best mesh wifi for broadband router</t>
+          <t>broadband for universal credit</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1300</v>
+        <v>720</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>34</v>
+        <v>27.5</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14608,49 +14618,49 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
+          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Affordability</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>broadband for universal credit</t>
+          <t>gigaclear broadband</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>720</v>
+        <v>2400</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>58.2</v>
+        <v>56.9</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>27.5</v>
+        <v>27.9</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14670,12 +14680,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
+          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -14690,14 +14700,14 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>gigaclear broadband</t>
+          <t>cuckoo broadband broadband</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -14705,14 +14715,14 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.9</v>
+        <v>56.5</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14732,49 +14742,49 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
+          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Deals &amp; pricing</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Provider page</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>cuckoo broadband broadband</t>
+          <t>black friday broadband deals</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2900</v>
+        <v>5400</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>27.9</v>
+        <v>37</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14794,49 +14804,49 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
+          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Deals &amp; pricing</t>
+          <t>Provider brand</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Provider page</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>black friday broadband deals</t>
+          <t>shell energy broadband broadband</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14856,31 +14866,31 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
+          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Provider brand</t>
+          <t>Trust &amp; research</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Provider page</t>
+          <t>Research page</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>shell energy broadband broadband</t>
+          <t>best customer service broadband provider</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3600</v>
+        <v>880</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>27</v>
@@ -14891,14 +14901,14 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>55.7</v>
+        <v>55.1</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
+          <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
@@ -14918,12 +14928,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
+          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -14933,1294 +14943,1292 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Research page</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>best customer service broadband provider</t>
+          <t>broadband complaints ombudsman</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 26); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>hyperoptic vs youfibre broadband</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 14); niche combined demand (140/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>broadband providers sheffield</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>590</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 19); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>static ip business broadband</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 24); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Student broadband by university city: short-term and rolling deals</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Use cases &amp; lifestyle</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>student broadband cities guide</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 18); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers edinburgh</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 21); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>small office broadband setup</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 22); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>bt vs plusnet broadband</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 19); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>broadband providers glasgow</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
         <v>880</v>
       </c>
-      <c r="J13" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="J21" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Planned — not live</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="L21" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Trust &amp; research</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers liverpool</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Use cases &amp; lifestyle</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>broadband complaints ombudsman</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>broadband for landlords hmo</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers leeds</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 23); strong combined demand (1,000/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>ee vs talktalk broadband</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers bristol</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 24); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>broadband providers birmingham</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 25); strong combined demand (1,600/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Postcode &amp; location</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>City hub</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>broadband providers manchester</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 26); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Leased line cost UK: what small businesses actually pay</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>leased line cost uk</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J29" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 30); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Alternative access</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>starlink vs openreach broadband</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>590</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 24); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>virgin media vs sky broadband</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>880</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 25); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>January broadband deals UK: new-year switching guide</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Deals &amp; pricing</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>january broadband deals</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 28); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Interactive tool</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>broadband cost per mbps calculator</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>youfibre broadband</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>4400</v>
+      </c>
+      <c r="J34" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 26); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Provider vs comparison</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Comparison page</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>hyperoptic vs youfibre broadband</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 14); niche combined demand (140/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>broadband providers sheffield</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>590</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 19); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Business broadband</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>static ip business broadband</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>480</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 24); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Use cases &amp; lifestyle</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>student broadband cities guide</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>320</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 18); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>broadband providers edinburgh</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>720</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 21); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Business broadband</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>small office broadband setup</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 22); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr"/>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Provider vs comparison</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Comparison page</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>bt vs plusnet broadband</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 19); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>broadband providers glasgow</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>880</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>broadband providers liverpool</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>880</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Use cases &amp; lifestyle</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>broadband for landlords hmo</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>480</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>broadband providers leeds</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 23); strong combined demand (1,000/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Provider vs comparison</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Comparison page</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>ee vs talktalk broadband</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>broadband providers bristol</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 24); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr"/>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>broadband providers birmingham</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 25); strong combined demand (1,600/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Postcode &amp; location</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>City hub</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>broadband providers manchester</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 26); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Business broadband</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>leased line cost uk</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 30); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Alternative access</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>starlink vs openreach broadband</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>590</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 24); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Provider vs comparison</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Comparison page</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>virgin media vs sky broadband</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>880</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 25); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>January broadband deals UK: new-year switching guide</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Deals &amp; pricing</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>january broadband deals</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 28); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>youfibre broadband</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n">
+      <c r="L34" s="4" t="n">
         <v>56.6</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="M34" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); strong combined demand (4,400/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>

--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>None supplied</t>
+          <t>https://docs.google.com/spreadsheets/d/1_IeyaXe1fSbXmV8Z4MdVOigMIz-cgK2h/edit</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10163</v>
+        <v>10416</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>9058</v>
+        <v>9062</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -13764,19 +13764,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>KT1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Kingston upon Thames ( KT1 )</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>8685</v>
-      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
     </row>
@@ -13796,19 +13786,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>CR0 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Croydon ( CR0 )</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>8603</v>
-      </c>
+      <c r="D143" s="3" t="inlineStr"/>
+      <c r="E143" s="3" t="inlineStr"/>
+      <c r="F143" s="3" t="inlineStr"/>
       <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="3" t="inlineStr"/>
     </row>
@@ -13828,19 +13808,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>HA1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Harrow ( HA1 )</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>8130</v>
-      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
     </row>
@@ -13860,19 +13830,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>UB1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Southall ( UB1 )</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>8130</v>
-      </c>
+      <c r="D145" s="3" t="inlineStr"/>
+      <c r="E145" s="3" t="inlineStr"/>
+      <c r="F145" s="3" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
     </row>
@@ -13892,19 +13852,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>EN1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Enfield ( EN1 )</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>8130</v>
-      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
     </row>
@@ -13924,19 +13874,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>RM1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Romford ( RM1 )</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>8130</v>
-      </c>
+      <c r="D147" s="3" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr"/>
+      <c r="F147" s="3" t="inlineStr"/>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr"/>
     </row>
@@ -13956,19 +13896,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>DA1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Dartford ( DA1 )</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>8134</v>
-      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
     </row>
@@ -13988,19 +13918,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>ME1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Rochester ( ME1 )</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>7641</v>
-      </c>
+      <c r="D149" s="3" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr"/>
+      <c r="F149" s="3" t="inlineStr"/>
       <c r="G149" s="3" t="inlineStr"/>
       <c r="H149" s="3" t="inlineStr"/>
     </row>
@@ -14020,19 +13940,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>SL1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Slough ( SL1 )</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>8134</v>
-      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
     </row>
@@ -14052,19 +13962,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>RG1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Reading Town Centre ( RG1 )</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>8705</v>
-      </c>
+      <c r="D151" s="3" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr"/>
+      <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="3" t="inlineStr"/>
     </row>
@@ -14084,19 +13984,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>GU1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Guildford ( GU1 )</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>8134</v>
-      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
     </row>
@@ -14116,19 +14006,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>MK1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Milton Keynes ( MK1 )</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>8175</v>
-      </c>
+      <c r="D153" s="3" t="inlineStr"/>
+      <c r="E153" s="3" t="inlineStr"/>
+      <c r="F153" s="3" t="inlineStr"/>
       <c r="G153" s="3" t="inlineStr"/>
       <c r="H153" s="3" t="inlineStr"/>
     </row>
@@ -14148,19 +14028,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>LU1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Luton ( LU1 )</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>8130</v>
-      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr"/>
     </row>
@@ -14180,19 +14050,9 @@
           <t>Postcode prefix page</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>SG1 Broadband Deals | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>Best Broadband Deals in Stevenage ( SG1 )</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>8130</v>
-      </c>
+      <c r="D155" s="3" t="inlineStr"/>
+      <c r="E155" s="3" t="inlineStr"/>
+      <c r="F155" s="3" t="inlineStr"/>
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="3" t="inlineStr"/>
     </row>

--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <strike val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -81,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -90,6 +96,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,7 +613,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -755,7 +767,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M148"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -9232,7 +9244,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -11290,7 +11302,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -11381,1914 +11393,1980 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>hyperoptic vs youfibre broadband</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="4" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 14); niche combined demand (140/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>broadband providers sheffield</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="5" t="n">
         <v>590</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="5" t="n">
         <v>66.8</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 19); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Business broadband</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>static ip business broadband</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="4" t="n">
         <v>66.3</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="4" t="n">
         <v>46.1</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Use cases &amp; lifestyle</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>student broadband cities guide</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="5" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="5" t="n">
         <v>36.2</v>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 18); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>broadband providers edinburgh</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="4" t="n">
         <v>720</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="4" t="n">
         <v>65.8</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 21); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Business broadband</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>small office broadband setup</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="5" t="n">
         <v>390</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="5" t="n">
         <v>65.8</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="5" t="n">
         <v>41.9</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 22); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>bt vs plusnet broadband</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="4" t="n">
         <v>320</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="4" t="n">
         <v>65.5</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 19); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>broadband providers glasgow</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="5" t="n">
         <v>880</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="5" t="n">
         <v>65.5</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="5" t="n">
         <v>40.2</v>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>broadband providers liverpool</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="4" t="n">
         <v>880</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" s="4" t="n">
         <v>65.5</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" s="4" t="n">
         <v>40.1</v>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Use cases &amp; lifestyle</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>broadband for landlords hmo</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="5" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/leeds</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>broadband providers leeds</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" s="4" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" s="4" t="n">
         <v>40.3</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 23); strong combined demand (1,000/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>ee vs talktalk broadband</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="5" t="n">
         <v>390</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="5" t="n">
         <v>36.4</v>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/bristol</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>broadband providers bristol</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" s="4" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" s="4" t="n">
         <v>40.8</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>broadband providers birmingham</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="5" t="n">
         <v>64.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="5" t="n">
         <v>41.1</v>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 25); strong combined demand (1,600/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/manchester</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Broadband providers in Manchester: coverage and best deals</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>broadband providers manchester</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="4" t="n">
         <v>1900</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" s="4" t="n">
         <v>64.2</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" s="4" t="n">
         <v>41.2</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Leased line cost UK: what small businesses actually pay</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Business broadband</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>leased line cost uk</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 30); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Alternative access</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>starlink vs openreach broadband</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>590</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 24); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Provider vs comparison</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Comparison page</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>virgin media vs sky broadband</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>880</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 25); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>January broadband deals UK: new-year switching guide</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Deals &amp; pricing</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>january broadband deals</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 28); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Interactive tool</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>broadband cost per mbps calculator</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Business broadband</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/onestream</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>onestream broadband</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>No credit check broadband in the UK: options and what to expect</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Affordability</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>leased line cost uk</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>no credit check broadband</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/brsk</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>brsk broadband</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; speeds</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>fttp vs fttc explained</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>880</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Technology &amp; speeds</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>best mesh wifi for broadband router</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Affordability</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>broadband for universal credit</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="J27" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>gigaclear broadband</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L17" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 30); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Alternative access</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L28" s="4" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>youfibre broadband</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 26); strong combined demand (4,400/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>cuckoo broadband broadband</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Deals &amp; pricing</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>starlink vs openreach broadband</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>590</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>black friday broadband deals</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>5400</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Provider brand</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Provider page</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>shell energy broadband broadband</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>3600</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 24); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Provider vs comparison</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Comparison page</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>virgin media vs sky broadband</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
+      <c r="L32" s="4" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Trust &amp; research</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Research page</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>best customer service broadband provider</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
         <v>880</v>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J33" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 25); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>January broadband deals UK: new-year switching guide</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Deals &amp; pricing</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L33" s="5" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Built, live and deployed on Vercel</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; research</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>january broadband deals</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>broadband complaints ombudsman</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 28); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Interactive tool</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>broadband cost per mbps calculator</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/onestream</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>onestream broadband</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>880</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Affordability</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>no credit check broadband</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/brsk</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>brsk broadband</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Technology &amp; speeds</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>fttp vs fttc explained</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Technology &amp; speeds</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>best mesh wifi for broadband router</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Affordability</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>broadband for universal credit</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>720</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>gigaclear broadband</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>youfibre broadband</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 26); strong combined demand (4,400/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>cuckoo broadband broadband</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Deals &amp; pricing</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>black friday broadband deals</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>5400</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Provider brand</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Provider page</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>shell energy broadband broadband</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Trust &amp; research</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Research page</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>best customer service broadband provider</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Planned — live check unavailable</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Trust &amp; research</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Guide</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>broadband complaints ombudsman</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
+      <c r="L34" s="4" t="n">
         <v>54.7</v>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="M34" s="4" t="n">
         <v>25.9</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
@@ -13310,7 +13388,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -13720,7 +13798,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -14217,7 +14295,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="3" t="n"/>
@@ -14261,7 +14339,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="2" t="n"/>
@@ -14305,7 +14383,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="3" t="n"/>
@@ -14349,7 +14427,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="2" t="n"/>
@@ -14393,7 +14471,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -14437,7 +14515,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="2" t="n"/>
@@ -14481,7 +14559,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="3" t="n"/>
@@ -14525,7 +14603,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="2" t="n"/>
@@ -14569,7 +14647,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="3" t="n"/>
@@ -14613,7 +14691,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="2" t="n"/>
@@ -14657,7 +14735,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="3" t="n"/>
@@ -14701,7 +14779,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="2" t="n"/>
@@ -14745,7 +14823,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="3" t="n"/>
@@ -14789,7 +14867,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="2" t="n"/>
@@ -14833,7 +14911,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
@@ -14877,7 +14955,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="2" t="n"/>
@@ -14969,7 +15047,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="2" t="n"/>
@@ -15013,7 +15091,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="3" t="n"/>
@@ -15057,7 +15135,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="2" t="n"/>
@@ -15193,7 +15271,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="3" t="n"/>
@@ -15241,7 +15319,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="2" t="n"/>
@@ -15285,7 +15363,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="3" t="n"/>
@@ -15373,7 +15451,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="3" t="n"/>
@@ -15417,7 +15495,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="2" t="n"/>
@@ -15461,7 +15539,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J35" s="3" t="n"/>
@@ -15505,7 +15583,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="2" t="n"/>
@@ -15593,7 +15671,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J38" s="2" t="n"/>
@@ -15637,7 +15715,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J39" s="3" t="n"/>
@@ -15681,7 +15759,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J40" s="2" t="n"/>
@@ -15769,7 +15847,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J42" s="2" t="n"/>
@@ -15813,7 +15891,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J43" s="3" t="n"/>
@@ -15857,7 +15935,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J44" s="2" t="n"/>
@@ -15949,7 +16027,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J46" s="2" t="n"/>
@@ -16591,7 +16669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16683,54 +16761,58 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>growth-awin-advertiser-outreach</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Continue selective Awin advertiser outreach</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -16738,33 +16820,33 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>page-postcode/sheffield</t>
+          <t>feat-review-aggregation-module</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Broadband providers in Sheffield: coverage and best deals</t>
+          <t>Real review-aggregation trust module</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>66.8</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -16774,10 +16856,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n"/>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
@@ -16788,2255 +16874,593 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>page-guides/static-ip-business-broadband-explained</t>
+          <t>ops-adsense-site-review</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Static IP business broadband: when you need one and how much it costs</t>
+          <t>Complete AdSense site review and authorisation monitoring</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>66.3</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46.1</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n"/>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/student-broadband-by-university-city</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>audit-city-hub-thinness</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Content audit</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Student broadband by university city: short-term and rolling deals</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify each new city hub has a genuinely local fact</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>data/priority-pages.ts city entries</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/edinburgh</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>growth-original-research-outreach</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Edinburgh: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Run original-research outreach and digital PR</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>/research/uk-broadband-customer-satisfaction</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Research page and source methodology are live</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>growth-quarterly-data-reprioritisation</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/small-office-broadband-setup-uk</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Next-quarter decision log</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>ops-conversion-reporting-loop and sufficient observation period</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Price-drop alerts</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>New subscription flow + data/provider-live-deals.json</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Email delivery provider</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>audit-core-web-vitals-reporting</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide template performance report</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Field data or representative lab baselines</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>audit-mobile-checkout-flow</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>UX audit</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Mobile checkout-flow audit</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Sitewide mobile layout</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Mobile analytics/drop-off data</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>audit-broken-links-redirects</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Sitewide crawl and redirect report</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>bet-annual-research-report</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Small office broadband setup: routers, backup and support checklist</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/compare/bt-vs-plusnet</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>New annual research page + methodology extension</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>bet-componentise-interactive-layer</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>components/</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>BT vs Plusnet broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>page-postcode/glasgow</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Broadband providers in Glasgow: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/liverpool</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Liverpool: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/leeds</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Leeds: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/compare/ee-vs-talktalk</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/bristol</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Bristol: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>page-postcode/birmingham</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Broadband providers in Birmingham: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>page-postcode/manchester</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Broadband providers in Manchester: coverage and best deals</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Leased line cost UK: what small businesses actually pay</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>January broadband deals UK: new-year switching guide</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>growth-awin-advertiser-outreach</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Partnerships</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Continue selective Awin advertiser outreach</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Awin publisher 2942019 and partner application log</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Current audience evidence and compliant commercial pages</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>page-tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Broadband cost calculator: true monthly and contract-length cost</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/onestream</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Onestream — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/onestream</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>No credit check broadband in the UK: options and what to expect</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>feat-review-aggregation-module</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Real review-aggregation trust module</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>New shared component, used on provider + comparison pages</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/brsk</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Brsk — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/brsk</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>FTTP vs FTTC: what the difference means for your speed</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ops-adsense-site-review</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>AdSense status and /ads.txt</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Google site-review processing</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/youfibre</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>page-providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>audit-city-hub-thinness</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Content audit</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Verify each new city hub has a genuinely local fact</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>data/priority-pages.ts city entries</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>page-guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>page-providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>page-research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>growth-original-research-outreach</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Run original-research outreach and digital PR</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>/research/uk-broadband-customer-satisfaction</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>Research page and source methodology are live</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>growth-quarterly-data-reprioritisation</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Next-quarter decision log</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>ops-conversion-reporting-loop and sufficient observation period</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>feat-price-drop-alerts</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Price-drop alerts</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>New subscription flow + data/provider-live-deals.json</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>Email delivery provider</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>audit-core-web-vitals-reporting</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Sitewide template performance report</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Field data or representative lab baselines</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>audit-mobile-checkout-flow</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>UX audit</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Mobile checkout-flow audit</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Sitewide mobile layout</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>Mobile analytics/drop-off data</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>audit-broken-links-redirects</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Crawlability</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Add routine broken-link and redirect reporting</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Sitewide crawl and redirect report</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>bet-annual-research-report</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Annual 'State of UK Broadband' research report</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>New annual research page + methodology extension</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>bet-componentise-interactive-layer</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>components/</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>bet-decouple-content-from-code</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Bigger bet</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Decouple guide content from code deploys</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N47"/>

--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -9462,15 +9462,29 @@
           <t>Interactive tool</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Internet Speed Test UK: Check Broadband Speed Free | BroadbandPicker</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Broadband speed test</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1360</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>broadband speed test, check my broadband speed</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>internet speed test, broadband speed test, free internet speed test, broadband speed test UK, download and upload speed test, internet speed test ping, Wi-Fi speed test vs Ethernet</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Live production audit passed 2026-08-23. Added jitter, responsive and accessible results, GA4 journey events, updated methodology, keyword research and competitor evidence. Vercel deployment dpl_FdGUagz6k8xA9qVLV6LRaz66PGVn.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">

--- a/docs/broadbandpicker-keyword-mapping.xlsx
+++ b/docs/broadbandpicker-keyword-mapping.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Content Gap Roadmap'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cluster Summary'!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Methodology'!$A$1:$B$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Master Build Tracker'!$A$1:$L$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Pending Build Priority'!$A$1:$N$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Master Build Tracker'!$A$1:$L$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Pending Build Priority'!$A$1:$N$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,12 +44,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <strike val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -87,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -96,12 +90,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -280,8 +268,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="MasterBuildTrackerTable" displayName="MasterBuildTrackerTable" ref="A1:L60" headerRowCount="1">
-  <autoFilter ref="A1:L60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="MasterBuildTrackerTable" displayName="MasterBuildTrackerTable" ref="A1:L64" headerRowCount="1">
+  <autoFilter ref="A1:L64"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -301,8 +289,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N47" headerRowCount="1">
-  <autoFilter ref="A1:N47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PendingBuildPriorityTable" displayName="PendingBuildPriorityTable" ref="A1:N48" headerRowCount="1">
+  <autoFilter ref="A1:N48"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Pending Rank"/>
     <tableColumn id="2" name="Item ID"/>
@@ -613,7 +601,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -675,7 +663,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1_IeyaXe1fSbXmV8Z4MdVOigMIz-cgK2h/edit</t>
+          <t>None supplied</t>
         </is>
       </c>
     </row>
@@ -767,7 +755,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M148"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -9244,7 +9232,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -9462,29 +9450,15 @@
           <t>Interactive tool</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Internet Speed Test UK: Check Broadband Speed Free | BroadbandPicker</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Broadband speed test</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1360</v>
-      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>internet speed test, broadband speed test, free internet speed test, broadband speed test UK, download and upload speed test, internet speed test ping, Wi-Fi speed test vs Ethernet</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Live production audit passed 2026-08-23. Added jitter, responsive and accessible results, GA4 journey events, updated methodology, keyword research and competitor evidence. Vercel deployment dpl_FdGUagz6k8xA9qVLV6LRaz66PGVn.</t>
-        </is>
-      </c>
+          <t>broadband speed test, check my broadband speed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11316,7 +11290,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -11407,1980 +11381,1914 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>hyperoptic vs youfibre broadband</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="2" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 14); niche combined demand (140/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>broadband providers sheffield</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 19); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Business broadband</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>static ip business broadband</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="2" t="n">
         <v>66.3</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="2" t="n">
         <v>46.1</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Student broadband by university city: short-term and rolling deals</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Use cases &amp; lifestyle</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>student broadband cities guide</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="3" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 18); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Broadband providers in Edinburgh: coverage and best deals</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>broadband providers edinburgh</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="2" t="n">
         <v>720</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="2" t="n">
         <v>65.8</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 21); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Small office broadband setup: routers, backup and support checklist</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Business broadband</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>small office broadband setup</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" s="3" t="n">
         <v>65.8</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="3" t="n">
         <v>41.9</v>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 22); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>BT vs Plusnet broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>bt vs plusnet broadband</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="2" t="n">
         <v>65.5</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 19); useful combined demand (320/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Broadband providers in Glasgow: coverage and best deals</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>broadband providers glasgow</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="3" t="n">
         <v>65.5</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="3" t="n">
         <v>40.2</v>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Broadband providers in Liverpool: coverage and best deals</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>broadband providers liverpool</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="2" t="n">
         <v>880</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="2" t="n">
         <v>65.5</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="2" t="n">
         <v>40.1</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 22); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Broadband for landlords and HMOs: what to set up and who pays</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Use cases &amp; lifestyle</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>broadband for landlords hmo</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="L11" s="3" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M11" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); useful combined demand (480/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/leeds</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Broadband providers in Leeds: coverage and best deals</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>broadband providers leeds</t>
         </is>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="2" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="2" t="n">
         <v>40.3</v>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 23); strong combined demand (1,000/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>EE vs TalkTalk broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>ee vs talktalk broadband</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I13" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L13" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="M13" s="3" t="n">
         <v>36.4</v>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); useful combined demand (390/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/bristol</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Broadband providers in Bristol: coverage and best deals</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>broadband providers bristol</t>
         </is>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="2" t="n">
         <v>1300</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="2" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="2" t="n">
         <v>40.8</v>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Broadband providers in Birmingham: coverage and best deals</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>broadband providers birmingham</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" s="3" t="n">
         <v>64.5</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="M15" s="3" t="n">
         <v>41.1</v>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 25); strong combined demand (1,600/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/postcode/manchester</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Broadband providers in Manchester: coverage and best deals</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Postcode &amp; location</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>City hub</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>broadband providers manchester</t>
         </is>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="2" t="n">
         <v>64.2</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="M16" s="2" t="n">
         <v>41.2</v>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Leased line cost UK: what small businesses actually pay</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Business broadband</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>leased line cost uk</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17" s="3" t="n">
         <v>63.3</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="M17" s="3" t="n">
         <v>58.6</v>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 30); useful combined demand (720/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Alternative access</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>starlink vs openreach broadband</t>
         </is>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="2" t="n">
         <v>590</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="2" t="n">
         <v>62.9</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="M18" s="2" t="n">
         <v>35.4</v>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); useful combined demand (590/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Provider vs comparison</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Comparison page</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>virgin media vs sky broadband</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I19" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J19" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L19" s="3" t="n">
         <v>62.8</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="M19" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 25); useful combined demand (880/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>January broadband deals UK: new-year switching guide</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Deals &amp; pricing</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>january broadband deals</t>
         </is>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="2" t="n">
         <v>1300</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="2" t="n">
         <v>61.7</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="2" t="n">
         <v>36.9</v>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 28); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Broadband cost calculator: true monthly and contract-length cost</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Interactive tool</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>broadband cost per mbps calculator</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J21" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="L21" s="3" t="n">
         <v>59.9</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="M21" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 16); niche combined demand (210/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/onestream</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Onestream — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>onestream broadband</t>
         </is>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="2" t="n">
         <v>880</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="2" t="n">
         <v>59.4</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="M22" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 18); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>No credit check broadband in the UK: options and what to expect</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Affordability</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>no credit check broadband</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L23" s="3" t="n">
         <v>59.3</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="M23" s="3" t="n">
         <v>34.8</v>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Moderate opportunity (difficulty 32); strong combined demand (1,900/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/brsk</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Brsk — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>brsk broadband</t>
         </is>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="2" t="n">
         <v>28.5</v>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); strong combined demand (1,900/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>FTTP vs FTTC: what the difference means for your speed</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Technology &amp; speeds</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>fttp vs fttc explained</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I25" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" s="3" t="n">
         <v>58.4</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="M25" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Technology &amp; speeds</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>best mesh wifi for broadband router</t>
         </is>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="2" t="n">
         <v>1300</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="2" t="n">
         <v>58.4</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="M26" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Moderate opportunity (difficulty 33); strong combined demand (1,300/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Affordability</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>broadband for universal credit</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I27" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="3" t="n">
         <v>58.2</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="M27" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Very easy opportunity (difficulty 20); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>gigaclear broadband</t>
         </is>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="2" t="n">
         <v>2400</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="2" t="n">
         <v>56.9</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="M28" s="2" t="n">
         <v>27.9</v>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 24); strong combined demand (2,400/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/youfibre</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>YouFibre — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>youfibre broadband</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I29" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="3" t="n">
         <v>56.6</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="M29" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); strong combined demand (4,400/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>cuckoo broadband broadband</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" s="2" t="n">
         <v>2900</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="2" t="n">
         <v>56.5</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="M30" s="2" t="n">
         <v>27.9</v>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 25); strong combined demand (2,900/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Black Friday broadband deals UK: what to expect and how to compare</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Deals &amp; pricing</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>black friday broadband deals</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="I31" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="J31" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="L31" s="3" t="n">
         <v>55.8</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="M31" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Competitive opportunity (difficulty 42); strong combined demand (5,400/mo); commercial intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Provider brand</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Provider page</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>shell energy broadband broadband</t>
         </is>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="2" t="n">
         <v>3600</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="2" t="n">
         <v>55.7</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="M32" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 27); strong combined demand (3,600/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Trust &amp; research</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Research page</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>best customer service broadband provider</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L33" s="3" t="n">
         <v>55.1</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="M33" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 27); useful combined demand (880/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Built, live and deployed on Vercel</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Planned — live check unavailable</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Trust &amp; research</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>broadband complaints ombudsman</t>
         </is>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="2" t="n">
         <v>720</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J34" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="2" t="n">
         <v>54.7</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="M34" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Easy opportunity (difficulty 26); useful combined demand (720/mo); supporting intent; covers 1 mapped keyword.</t>
         </is>
@@ -13402,7 +13310,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -13812,7 +13720,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -13953,7 +13861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14309,7 +14217,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J7" s="3" t="n"/>
@@ -14353,7 +14261,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J8" s="2" t="n"/>
@@ -14397,7 +14305,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J9" s="3" t="n"/>
@@ -14441,7 +14349,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J10" s="2" t="n"/>
@@ -14485,7 +14393,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -14529,7 +14437,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J12" s="2" t="n"/>
@@ -14573,7 +14481,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J13" s="3" t="n"/>
@@ -14617,7 +14525,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J14" s="2" t="n"/>
@@ -14661,7 +14569,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J15" s="3" t="n"/>
@@ -14705,7 +14613,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J16" s="2" t="n"/>
@@ -14749,7 +14657,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J17" s="3" t="n"/>
@@ -14793,7 +14701,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J18" s="2" t="n"/>
@@ -14837,7 +14745,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J19" s="3" t="n"/>
@@ -14881,7 +14789,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J20" s="2" t="n"/>
@@ -14925,7 +14833,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
@@ -14969,7 +14877,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J22" s="2" t="n"/>
@@ -15061,7 +14969,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J24" s="2" t="n"/>
@@ -15105,7 +15013,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J25" s="3" t="n"/>
@@ -15149,7 +15057,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J26" s="2" t="n"/>
@@ -15285,7 +15193,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J29" s="3" t="n"/>
@@ -15333,7 +15241,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J30" s="2" t="n"/>
@@ -15377,7 +15285,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J31" s="3" t="n"/>
@@ -15465,7 +15373,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J33" s="3" t="n"/>
@@ -15509,7 +15417,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J34" s="2" t="n"/>
@@ -15553,7 +15461,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J35" s="3" t="n"/>
@@ -15597,7 +15505,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J36" s="2" t="n"/>
@@ -15685,7 +15593,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J38" s="2" t="n"/>
@@ -15729,7 +15637,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J39" s="3" t="n"/>
@@ -15773,7 +15681,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J40" s="2" t="n"/>
@@ -15861,7 +15769,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J42" s="2" t="n"/>
@@ -15905,7 +15813,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J43" s="3" t="n"/>
@@ -15949,7 +15857,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J44" s="2" t="n"/>
@@ -16010,38 +15918,38 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+          <t>feat-contact-form-email-delivery</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Broadband complaints and the ombudsman: your UK rights</t>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J46" s="2" t="n"/>
@@ -16054,12 +15962,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>growth-original-research-outreach</t>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -16069,23 +15977,23 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Run original-research outreach and digital PR</t>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>68</v>
+        <v>25.9</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J47" s="3" t="n"/>
@@ -16098,29 +16006,29 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>growth-quarterly-data-reprioritisation</t>
+          <t>growth-original-research-outreach</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
+          <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -16129,7 +16037,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J48" s="2" t="n"/>
@@ -16142,29 +16050,29 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>feat-homepage-visual-redesign</t>
+          <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Homepage visual redesign: illustrations + interactivity</t>
+          <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -16173,7 +16081,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J49" s="3" t="n"/>
@@ -16186,7 +16094,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>feat-mobile-cross-device-navigation</t>
+          <t>feat-postcode-journey-personalisation</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -16201,14 +16109,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Mobile and cross-device navigation overhaul</t>
+          <t>Postcode-aware personalisation across the customer journey, free tier only</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -16230,7 +16138,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>feat-mega-menu-navigation</t>
+          <t>feat-homepage-visual-redesign</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -16245,14 +16153,14 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Detailed mega-menu navigation</t>
+          <t>Homepage visual redesign: illustrations + interactivity</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -16274,7 +16182,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>feat-price-drop-alerts</t>
+          <t>feat-mobile-cross-device-navigation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -16284,19 +16192,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Price-drop alerts</t>
+          <t>Mobile and cross-device navigation overhaul</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -16305,7 +16213,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J52" s="2" t="n"/>
@@ -16318,7 +16226,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>feat-page-type-ux-redesign</t>
+          <t>feat-mega-menu-navigation</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -16333,14 +16241,14 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
+          <t>Detailed mega-menu navigation</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -16362,7 +16270,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>feat-footer-logo-interactivity</t>
+          <t>feat-animated-interactive-mobile-menu</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -16377,18 +16285,18 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Footer logo placement and interactive elements</t>
+          <t>Animated, interactive mobile menu with click-outside-to-close</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -16398,11 +16306,7 @@
       </c>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
-        </is>
-      </c>
+      <c r="L54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -16410,29 +16314,29 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>audit-core-web-vitals-reporting</t>
+          <t>feat-price-drop-alerts</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Establish monthly Core Web Vitals reporting by template</t>
+          <t>Price-drop alerts</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -16454,12 +16358,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>audit-mobile-checkout-flow</t>
+          <t>feat-page-type-ux-redesign</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UX audit</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -16469,14 +16373,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Mobile checkout-flow audit</t>
+          <t>Page-type UX redesign: deals, providers, guides, postcode hub</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -16485,7 +16389,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J56" s="2" t="n"/>
@@ -16498,29 +16402,29 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>audit-broken-links-redirects</t>
+          <t>feat-footer-logo-interactivity</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Technical SEO</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Crawlability</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Add routine broken-link and redirect reporting</t>
+          <t>Footer logo placement and interactive elements</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -16529,12 +16433,16 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="n"/>
-      <c r="L57" s="3" t="n"/>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Follow-up 2026-08-23: added Instagram (@broadbandpicker) as a second social pill button next to X, same hover treatment.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -16542,33 +16450,33 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>bet-annual-research-report</t>
+          <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Technical SEO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Annual 'State of UK Broadband' research report</t>
+          <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -16586,38 +16494,38 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>bet-componentise-interactive-layer</t>
+          <t>ops-awin-publisher-api-integration</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Monetisation</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Componentise the interactive layer on accessible primitives</t>
+          <t>Direct Awin Publisher API access — programme status and link generation</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="3" t="n"/>
@@ -16630,33 +16538,33 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>bet-decouple-content-from-code</t>
+          <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Bigger bet</t>
+          <t>UX audit</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Decouple guide content from code deploys</t>
+          <t>Mobile checkout-flow audit</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -16668,8 +16576,184 @@
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
     </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>audit-broken-links-redirects</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Add routine broken-link and redirect reporting</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>bet-annual-research-report</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Annual 'State of UK Broadband' research report</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>bet-componentise-interactive-layer</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Componentise the interactive layer on accessible primitives</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>bet-decouple-content-from-code</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Bigger bet</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Decouple guide content from code deploys</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -16683,7 +16767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16775,58 +16859,54 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>growth-awin-advertiser-outreach</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Partnerships</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Monetisation</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Continue selective Awin advertiser outreach</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Awin publisher 2942019 and partner application log</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Current audience evidence and compliant commercial pages</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/compare/hyperoptic-vs-youfibre</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Hyperoptic vs YouFibre broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/hyperoptic-vs-youfibre</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -16834,33 +16914,33 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>feat-review-aggregation-module</t>
+          <t>page-postcode/sheffield</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Real review-aggregation trust module</t>
+          <t>Broadband providers in Sheffield: coverage and best deals</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>59</v>
+        <v>66.8</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very easy</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -16870,14 +16950,10 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>New shared component, used on provider + comparison pages</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>research/uk-broadband-customer-satisfaction methodology</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/postcode/sheffield</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
@@ -16888,596 +16964,2312 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ops-adsense-site-review</t>
+          <t>page-guides/static-ip-business-broadband-explained</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Monetisation</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Complete AdSense site review and authorisation monitoring</t>
+          <t>Static IP business broadband: when you need one and how much it costs</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58</v>
+        <v>66.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>55</v>
+        <v>46.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AdSense status and /ads.txt</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Google site-review processing</t>
-        </is>
-      </c>
+          <t>https://broadbandpicker.co.uk/guides/static-ip-business-broadband-explained</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Student broadband by university city: short-term and rolling deals</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/student-broadband-by-university-city</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Edinburgh: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/edinburgh</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Small office broadband setup: routers, backup and support checklist</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/small-office-broadband-setup-uk</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/compare/bt-vs-plusnet</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BT vs Plusnet broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/bt-vs-plusnet</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>page-postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Glasgow: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/glasgow</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Liverpool: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/liverpool</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Broadband for landlords and HMOs: what to set up and who pays</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-for-landlords-and-hmos-uk</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/leeds</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Leeds: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/leeds</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/compare/ee-vs-talktalk</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>EE vs TalkTalk broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/ee-vs-talktalk</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/bristol</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Bristol: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/bristol</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>page-postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Broadband providers in Birmingham: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/birmingham</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>page-postcode/manchester</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Broadband providers in Manchester: coverage and best deals</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/postcode/manchester</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Leased line cost UK: what small businesses actually pay</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/leased-line-cost-uk-explained</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Starlink vs fibre broadband: when satellite makes sense in the UK</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/starlink-vs-fibre-broadband-uk</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Virgin Media vs Sky broadband: which is better in 2026?</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/compare/virgin-media-vs-sky</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>January broadband deals UK: new-year switching guide</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/january-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>growth-awin-advertiser-outreach</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Continue selective Awin advertiser outreach</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Awin publisher 2942019 and partner application log</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Current audience evidence and compliant commercial pages</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>page-tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Broadband cost calculator: true monthly and contract-length cost</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/tools/broadband-cost-calculator</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Live at /tools/broadband-cost-calculator, committed and deployed 2026-08-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/onestream</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Onestream — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/onestream</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>No credit check broadband in the UK: options and what to expect</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/no-credit-check-broadband-uk</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>feat-review-aggregation-module</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Real review-aggregation trust module</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>New shared component, used on provider + comparison pages</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>research/uk-broadband-customer-satisfaction methodology</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/brsk</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Brsk — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/brsk</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>FTTP vs FTTC: what the difference means for your speed</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/fttp-vs-fttc-explained</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>page-guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Best mesh Wi-Fi systems to pair with your broadband router</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/best-mesh-wifi-for-your-broadband-router</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Cheaper broadband if you claim benefits: social tariffs explained</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-help-if-you-claim-benefits-uk</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ops-adsense-site-review</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Monetisation</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Complete AdSense site review and authorisation monitoring</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>AdSense status and /ads.txt</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Google site-review processing</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Gigaclear — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/gigaclear</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/youfibre</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>YouFibre — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/youfibre</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>page-providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Cuckoo Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/cuckoo</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>audit-city-hub-thinness</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Content audit</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Verify each new city hub has a genuinely local fact</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>data/priority-pages.ts city entries</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Black Friday broadband deals UK: what to expect and how to compare</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/black-friday-broadband-deals-uk</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>page-providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Shell Energy Broadband — plans, coverage and Awin-tracked deals</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/providers/shell-energy</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>page-research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Broadband customer service rankings: Ofcom-evidenced comparison</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/research/broadband-customer-service-rankings-uk</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>feat-contact-form-email-delivery</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Working contact form delivering to a real inbox, no third-party service</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>app/api/contact/route.ts, components/ContactForm.tsx, app/contact/page.tsx</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>CONTACT_SMTP_USER / CONTACT_SMTP_PASS Gmail App Password set in Vercel env vars</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>page-guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Broadband complaints and the ombudsman: your UK rights</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>growth-original-research-outreach</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Run original-research outreach and digital PR</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F40" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G40" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>/research/uk-broadband-customer-satisfaction</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Research page and source methodology are live</t>
         </is>
       </c>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>growth-quarterly-data-reprioritisation</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Reprioritise quarter two using GSC, engagement and affiliate evidence</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F41" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>Next-quarter decision log</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>ops-conversion-reporting-loop and sufficient observation period</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>feat-price-drop-alerts</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Functionality</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Price-drop alerts</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F42" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G42" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>New subscription flow + data/provider-live-deals.json</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Email delivery provider</t>
         </is>
       </c>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>audit-core-web-vitals-reporting</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Technical SEO</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Establish monthly Core Web Vitals reporting by template</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Sitewide template performance report</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>Field data or representative lab baselines</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>audit-mobile-checkout-flow</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UX audit</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Mobile checkout-flow audit</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F44" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G44" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Sitewide mobile layout</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Mobile analytics/drop-off data</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>audit-broken-links-redirects</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Technical SEO</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Crawlability</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Add routine broken-link and redirect reporting</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Sitewide crawl and redirect report</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>bet-annual-research-report</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Bigger bet</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Annual 'State of UK Broadband' research report</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F46" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G46" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>New annual research page + methodology extension</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>research/uk-broadband-customer-satisfaction methodology</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>bet-componentise-interactive-layer</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Bigger bet</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Functionality</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Componentise the interactive layer on accessible primitives</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F47" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>components/</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>feat-shortlist-compare-basket, feat-price-drop-alerts</t>
         </is>
       </c>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>bet-decouple-content-from-code</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Bigger bet</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Decouple guide content from code deploys</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F48" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G48" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>data/guides.ts, app/guides/[slug]/page.tsx</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>None, but easier before the guide count grows further</t>
         </is>
       </c>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N47"/>
+  <autoFilter ref="A1:N48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
